--- a/data/fmsForecastOutput/File1/RPT_RPT6487446224014EI_fmsForecastOutput.xlsx
+++ b/data/fmsForecastOutput/File1/RPT_RPT6487446224014EI_fmsForecastOutput.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMS Forecast Output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1875,43 +1875,43 @@
         </is>
       </c>
       <c r="C8" s="148" t="n">
-        <v>442.5127656309309</v>
+        <v>442.5127656309308</v>
       </c>
       <c r="D8" s="149" t="n">
-        <v>467.0539161019682</v>
+        <v>467.0539161019681</v>
       </c>
       <c r="E8" s="149" t="n">
-        <v>497.885757728417</v>
+        <v>497.8857577284169</v>
       </c>
       <c r="F8" s="149" t="n">
-        <v>525.7099837566025</v>
+        <v>525.7099837566024</v>
       </c>
       <c r="G8" s="150" t="n">
         <v>554.5901215023863</v>
       </c>
       <c r="H8" s="148" t="n">
-        <v>438.5914687043146</v>
+        <v>438.5914687043145</v>
       </c>
       <c r="I8" s="149" t="n">
-        <v>464.0499710971986</v>
+        <v>464.0499710971985</v>
       </c>
       <c r="J8" s="149" t="n">
-        <v>495.7543108239861</v>
+        <v>495.754310823986</v>
       </c>
       <c r="K8" s="149" t="n">
-        <v>524.5161427448651</v>
+        <v>524.516142744865</v>
       </c>
       <c r="L8" s="150" t="n">
         <v>554.4564960112424</v>
       </c>
       <c r="M8" s="151" t="n">
-        <v>49262485.89615832</v>
+        <v>49262485.89615831</v>
       </c>
       <c r="N8" s="152" t="n">
         <v>56909334.46022815</v>
       </c>
       <c r="O8" s="152" t="n">
-        <v>65589520.73185218</v>
+        <v>65589520.73185217</v>
       </c>
       <c r="P8" s="152" t="n">
         <v>74668629.94129071</v>
@@ -1925,43 +1925,43 @@
         </is>
       </c>
       <c r="T8" s="148" t="n">
-        <v>542.7165981449876</v>
+        <v>542.7165981449875</v>
       </c>
       <c r="U8" s="149" t="n">
-        <v>572.814915600792</v>
+        <v>572.8149156007918</v>
       </c>
       <c r="V8" s="149" t="n">
-        <v>610.6284059713884</v>
+        <v>610.6284059713882</v>
       </c>
       <c r="W8" s="149" t="n">
-        <v>644.7532278271009</v>
+        <v>644.7532278271008</v>
       </c>
       <c r="X8" s="150" t="n">
         <v>680.1730650130473</v>
       </c>
       <c r="Y8" s="148" t="n">
-        <v>537.9638116605025</v>
+        <v>537.9638116605023</v>
       </c>
       <c r="Z8" s="149" t="n">
-        <v>569.174105276084</v>
+        <v>569.1741052760838</v>
       </c>
       <c r="AA8" s="149" t="n">
-        <v>608.0451375670335</v>
+        <v>608.0451375670334</v>
       </c>
       <c r="AB8" s="149" t="n">
-        <v>643.306352309255</v>
+        <v>643.3063523092549</v>
       </c>
       <c r="AC8" s="150" t="n">
         <v>680.0111215034034</v>
       </c>
       <c r="AD8" s="151" t="n">
-        <v>49262485.89615832</v>
+        <v>49262485.89615831</v>
       </c>
       <c r="AE8" s="152" t="n">
         <v>56909334.46022815</v>
       </c>
       <c r="AF8" s="152" t="n">
-        <v>65589520.73185218</v>
+        <v>65589520.73185217</v>
       </c>
       <c r="AG8" s="152" t="n">
         <v>74668629.94129071</v>
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="C9" s="155" t="n">
-        <v>851.368099959485</v>
+        <v>851.3680999594849</v>
       </c>
       <c r="D9" s="156" t="n">
-        <v>889.1754653166771</v>
+        <v>889.175465316677</v>
       </c>
       <c r="E9" s="156" t="n">
-        <v>938.8343571104808</v>
+        <v>938.8343571104807</v>
       </c>
       <c r="F9" s="156" t="n">
-        <v>979.4055405063605</v>
+        <v>979.4055405063607</v>
       </c>
       <c r="G9" s="157" t="n">
         <v>1021.313500162778</v>
       </c>
       <c r="H9" s="155" t="n">
-        <v>843.2473733544037</v>
+        <v>843.2473733544036</v>
       </c>
       <c r="I9" s="156" t="n">
-        <v>882.6571928898776</v>
+        <v>882.6571928898775</v>
       </c>
       <c r="J9" s="156" t="n">
-        <v>933.934242711458</v>
+        <v>933.9342427114578</v>
       </c>
       <c r="K9" s="156" t="n">
-        <v>976.2956655293948</v>
+        <v>976.295665529395</v>
       </c>
       <c r="L9" s="157" t="n">
         <v>1020.207414946071</v>
@@ -2061,10 +2061,10 @@
         <v>25906464.01794768</v>
       </c>
       <c r="P9" s="159" t="n">
-        <v>28901815.03433855</v>
+        <v>28901815.03433856</v>
       </c>
       <c r="Q9" s="160" t="n">
-        <v>32912312.71435728</v>
+        <v>32912312.71435727</v>
       </c>
       <c r="S9" s="32" t="inlineStr">
         <is>
@@ -2072,34 +2072,34 @@
         </is>
       </c>
       <c r="T9" s="155" t="n">
-        <v>861.2299125315155</v>
+        <v>861.2299125315154</v>
       </c>
       <c r="U9" s="156" t="n">
-        <v>899.4752190695115</v>
+        <v>899.4752190695114</v>
       </c>
       <c r="V9" s="156" t="n">
-        <v>949.709334063983</v>
+        <v>949.7093340639829</v>
       </c>
       <c r="W9" s="156" t="n">
-        <v>990.7504732950587</v>
+        <v>990.7504732950588</v>
       </c>
       <c r="X9" s="157" t="n">
-        <v>1033.143873319077</v>
+        <v>1033.143873319076</v>
       </c>
       <c r="Y9" s="155" t="n">
-        <v>852.9490772297797</v>
+        <v>852.9490772297796</v>
       </c>
       <c r="Z9" s="156" t="n">
-        <v>892.828312908976</v>
+        <v>892.8283129089758</v>
       </c>
       <c r="AA9" s="156" t="n">
-        <v>944.712433558961</v>
+        <v>944.7124335589609</v>
       </c>
       <c r="AB9" s="156" t="n">
-        <v>987.5791200530347</v>
+        <v>987.5791200530349</v>
       </c>
       <c r="AC9" s="157" t="n">
-        <v>1032.01590305034</v>
+        <v>1032.015903050339</v>
       </c>
       <c r="AD9" s="158" t="n">
         <v>20742277.47422827</v>
@@ -2111,10 +2111,10 @@
         <v>25906464.01794768</v>
       </c>
       <c r="AG9" s="159" t="n">
-        <v>28901815.03433855</v>
+        <v>28901815.03433856</v>
       </c>
       <c r="AH9" s="160" t="n">
-        <v>32912312.71435728</v>
+        <v>32912312.71435727</v>
       </c>
       <c r="AJ9" s="39" t="n"/>
       <c r="AQ9" s="40" t="inlineStr">
@@ -2176,28 +2176,28 @@
         <v>541.0578579140043</v>
       </c>
       <c r="E10" s="162" t="n">
-        <v>574.2532559788649</v>
+        <v>574.2532559788648</v>
       </c>
       <c r="F10" s="162" t="n">
-        <v>603.7564054388478</v>
+        <v>603.7564054388477</v>
       </c>
       <c r="G10" s="163" t="n">
-        <v>634.4096624700483</v>
+        <v>634.4096624700481</v>
       </c>
       <c r="H10" s="161" t="n">
         <v>511.2902720635586</v>
       </c>
       <c r="I10" s="162" t="n">
-        <v>537.4926036767956</v>
+        <v>537.4926036767955</v>
       </c>
       <c r="J10" s="162" t="n">
-        <v>571.7014829126274</v>
+        <v>571.7014829126272</v>
       </c>
       <c r="K10" s="162" t="n">
-        <v>602.2913305069405</v>
+        <v>602.2913305069403</v>
       </c>
       <c r="L10" s="163" t="n">
-        <v>634.1653799219854</v>
+        <v>634.1653799219852</v>
       </c>
       <c r="M10" s="164" t="n">
         <v>70004763.37038659</v>
@@ -2206,7 +2206,7 @@
         <v>79941396.55383496</v>
       </c>
       <c r="O10" s="165" t="n">
-        <v>91495984.74979986</v>
+        <v>91495984.74979985</v>
       </c>
       <c r="P10" s="165" t="n">
         <v>103570444.9756293</v>
@@ -2220,22 +2220,22 @@
         </is>
       </c>
       <c r="T10" s="161" t="n">
-        <v>609.5073410707038</v>
+        <v>609.5073410707035</v>
       </c>
       <c r="U10" s="162" t="n">
-        <v>639.7542568901221</v>
+        <v>639.754256890122</v>
       </c>
       <c r="V10" s="162" t="n">
-        <v>679.3005711954512</v>
+        <v>679.3005711954511</v>
       </c>
       <c r="W10" s="162" t="n">
-        <v>714.371234912846</v>
+        <v>714.3712349128458</v>
       </c>
       <c r="X10" s="163" t="n">
-        <v>750.7947662495177</v>
+        <v>750.7947662495176</v>
       </c>
       <c r="Y10" s="161" t="n">
-        <v>604.0599394918383</v>
+        <v>604.0599394918381</v>
       </c>
       <c r="Z10" s="162" t="n">
         <v>635.5523431960946</v>
@@ -2244,10 +2244,10 @@
         <v>676.2848280677913</v>
       </c>
       <c r="AB10" s="162" t="n">
-        <v>712.6304847866073</v>
+        <v>712.6304847866071</v>
       </c>
       <c r="AC10" s="163" t="n">
-        <v>750.4876810423576</v>
+        <v>750.4876810423575</v>
       </c>
       <c r="AD10" s="164" t="n">
         <v>70004763.37038659</v>
@@ -2256,7 +2256,7 @@
         <v>79941396.55383496</v>
       </c>
       <c r="AF10" s="165" t="n">
-        <v>91495984.74979986</v>
+        <v>91495984.74979985</v>
       </c>
       <c r="AG10" s="165" t="n">
         <v>103570444.9756293</v>
@@ -2318,46 +2318,46 @@
         </is>
       </c>
       <c r="C11" s="155" t="n">
-        <v>839.5697332261661</v>
+        <v>839.569733226166</v>
       </c>
       <c r="D11" s="156" t="n">
-        <v>869.1720308384154</v>
+        <v>869.1720308384156</v>
       </c>
       <c r="E11" s="156" t="n">
         <v>902.4776259888125</v>
       </c>
       <c r="F11" s="156" t="n">
-        <v>926.3053022591147</v>
+        <v>926.3053022591148</v>
       </c>
       <c r="G11" s="157" t="n">
-        <v>947.9208742640594</v>
+        <v>947.9208742640598</v>
       </c>
       <c r="H11" s="155" t="n">
         <v>835.8046916596273</v>
       </c>
       <c r="I11" s="156" t="n">
-        <v>866.8998500101986</v>
+        <v>866.8998500101987</v>
       </c>
       <c r="J11" s="156" t="n">
         <v>901.7227626515989</v>
       </c>
       <c r="K11" s="156" t="n">
-        <v>926.3053022591147</v>
+        <v>926.3053022591148</v>
       </c>
       <c r="L11" s="157" t="n">
-        <v>947.9208742640594</v>
+        <v>947.9208742640598</v>
       </c>
       <c r="M11" s="158" t="n">
-        <v>7028916.928648426</v>
+        <v>7028916.928648427</v>
       </c>
       <c r="N11" s="159" t="n">
-        <v>7954622.429042895</v>
+        <v>7954622.429042897</v>
       </c>
       <c r="O11" s="159" t="n">
         <v>9050687.642787918</v>
       </c>
       <c r="P11" s="159" t="n">
-        <v>10270977.88884245</v>
+        <v>10270977.88884246</v>
       </c>
       <c r="Q11" s="160" t="n">
         <v>11865024.34886792</v>
@@ -2398,16 +2398,16 @@
         <v>1163.710699476845</v>
       </c>
       <c r="AD11" s="158" t="n">
-        <v>7028916.928648426</v>
+        <v>7028916.928648427</v>
       </c>
       <c r="AE11" s="159" t="n">
-        <v>7954622.429042895</v>
+        <v>7954622.429042897</v>
       </c>
       <c r="AF11" s="159" t="n">
         <v>9050687.642787918</v>
       </c>
       <c r="AG11" s="159" t="n">
-        <v>10270977.88884245</v>
+        <v>10270977.88884246</v>
       </c>
       <c r="AH11" s="160" t="n">
         <v>11865024.34886792</v>
@@ -2461,16 +2461,16 @@
         </is>
       </c>
       <c r="C12" s="161" t="n">
-        <v>534.7334842439762</v>
+        <v>534.7334842439761</v>
       </c>
       <c r="D12" s="162" t="n">
-        <v>560.1964490353657</v>
+        <v>560.1964490353656</v>
       </c>
       <c r="E12" s="162" t="n">
-        <v>593.6892815859178</v>
+        <v>593.6892815859177</v>
       </c>
       <c r="F12" s="162" t="n">
-        <v>623.3393238961999</v>
+        <v>623.3393238961997</v>
       </c>
       <c r="G12" s="163" t="n">
         <v>653.9381538014708</v>
@@ -2479,13 +2479,13 @@
         <v>530.0691431999252</v>
       </c>
       <c r="I12" s="162" t="n">
-        <v>556.6344884279861</v>
+        <v>556.634488427986</v>
       </c>
       <c r="J12" s="162" t="n">
         <v>591.1775248317653</v>
       </c>
       <c r="K12" s="162" t="n">
-        <v>621.9183539240885</v>
+        <v>621.9183539240884</v>
       </c>
       <c r="L12" s="163" t="n">
         <v>653.702030702886</v>
@@ -2511,31 +2511,31 @@
         </is>
       </c>
       <c r="T12" s="161" t="n">
-        <v>633.1139980360379</v>
+        <v>633.1139980360377</v>
       </c>
       <c r="U12" s="162" t="n">
         <v>663.8105782197864</v>
       </c>
       <c r="V12" s="162" t="n">
-        <v>703.8100657689646</v>
+        <v>703.8100657689645</v>
       </c>
       <c r="W12" s="162" t="n">
-        <v>739.1662744380424</v>
+        <v>739.166274438042</v>
       </c>
       <c r="X12" s="163" t="n">
         <v>775.6450094449848</v>
       </c>
       <c r="Y12" s="161" t="n">
-        <v>627.5997932131268</v>
+        <v>627.5997932131266</v>
       </c>
       <c r="Z12" s="162" t="n">
         <v>659.5897709514312</v>
       </c>
       <c r="AA12" s="162" t="n">
-        <v>700.8272263124741</v>
+        <v>700.827226312474</v>
       </c>
       <c r="AB12" s="162" t="n">
-        <v>737.4704909686481</v>
+        <v>737.4704909686477</v>
       </c>
       <c r="AC12" s="163" t="n">
         <v>775.3468456148613</v>
@@ -2603,22 +2603,22 @@
         </is>
       </c>
       <c r="C13" s="155" t="n">
-        <v>6249.23556082267</v>
+        <v>6249.235560822666</v>
       </c>
       <c r="D13" s="156" t="n">
-        <v>6361.676321627418</v>
+        <v>6361.676321627417</v>
       </c>
       <c r="E13" s="156" t="n">
         <v>6650.857041192839</v>
       </c>
       <c r="F13" s="156" t="n">
-        <v>6828.265131891069</v>
+        <v>6828.265131891067</v>
       </c>
       <c r="G13" s="157" t="n">
-        <v>7100.246859124853</v>
+        <v>7100.246859124851</v>
       </c>
       <c r="H13" s="155" t="n">
-        <v>6246.75416522321</v>
+        <v>6246.754165223206</v>
       </c>
       <c r="I13" s="156" t="n">
         <v>6359.39368784548</v>
@@ -2627,22 +2627,22 @@
         <v>6648.671161826152</v>
       </c>
       <c r="K13" s="156" t="n">
-        <v>6826.25819962299</v>
+        <v>6826.258199622987</v>
       </c>
       <c r="L13" s="157" t="n">
-        <v>7098.390276206895</v>
+        <v>7098.390276206893</v>
       </c>
       <c r="M13" s="158" t="n">
-        <v>58276613.37108948</v>
+        <v>58276613.37108944</v>
       </c>
       <c r="N13" s="159" t="n">
-        <v>66475290.19997282</v>
+        <v>66475290.19997281</v>
       </c>
       <c r="O13" s="159" t="n">
         <v>77352540.38490896</v>
       </c>
       <c r="P13" s="159" t="n">
-        <v>89878921.09664796</v>
+        <v>89878921.09664793</v>
       </c>
       <c r="Q13" s="160" t="n">
         <v>106324933.94423</v>
@@ -2653,46 +2653,46 @@
         </is>
       </c>
       <c r="T13" s="155" t="n">
-        <v>3793.881167961036</v>
+        <v>3793.881167961034</v>
       </c>
       <c r="U13" s="156" t="n">
-        <v>3862.143418723782</v>
+        <v>3862.143418723781</v>
       </c>
       <c r="V13" s="156" t="n">
-        <v>4037.703657319148</v>
+        <v>4037.703657319147</v>
       </c>
       <c r="W13" s="156" t="n">
-        <v>4145.407264871322</v>
+        <v>4145.407264871321</v>
       </c>
       <c r="X13" s="157" t="n">
-        <v>4310.526077074639</v>
+        <v>4310.526077074637</v>
       </c>
       <c r="Y13" s="155" t="n">
-        <v>3792.846909154865</v>
+        <v>3792.846909154862</v>
       </c>
       <c r="Z13" s="156" t="n">
-        <v>3861.192016308699</v>
+        <v>3861.192016308698</v>
       </c>
       <c r="AA13" s="156" t="n">
-        <v>4036.792590784938</v>
+        <v>4036.792590784937</v>
       </c>
       <c r="AB13" s="156" t="n">
-        <v>4144.570791947395</v>
+        <v>4144.570791947394</v>
       </c>
       <c r="AC13" s="157" t="n">
-        <v>4309.752276397318</v>
+        <v>4309.752276397317</v>
       </c>
       <c r="AD13" s="158" t="n">
-        <v>58276613.37108948</v>
+        <v>58276613.37108944</v>
       </c>
       <c r="AE13" s="159" t="n">
-        <v>66475290.19997282</v>
+        <v>66475290.19997281</v>
       </c>
       <c r="AF13" s="159" t="n">
         <v>77352540.38490896</v>
       </c>
       <c r="AG13" s="159" t="n">
-        <v>89878921.09664796</v>
+        <v>89878921.09664793</v>
       </c>
       <c r="AH13" s="160" t="n">
         <v>106324933.94423</v>
@@ -2746,13 +2746,13 @@
         </is>
       </c>
       <c r="C14" s="167" t="n">
-        <v>882.1591674302013</v>
+        <v>882.1591674302009</v>
       </c>
       <c r="D14" s="168" t="n">
-        <v>922.4377207128609</v>
+        <v>922.4377207128606</v>
       </c>
       <c r="E14" s="168" t="n">
-        <v>982.9253540965932</v>
+        <v>982.9253540965929</v>
       </c>
       <c r="F14" s="168" t="n">
         <v>1040.481383505881</v>
@@ -2761,19 +2761,19 @@
         <v>1101.009454223988</v>
       </c>
       <c r="H14" s="167" t="n">
-        <v>874.9073566573392</v>
+        <v>874.9073566573389</v>
       </c>
       <c r="I14" s="168" t="n">
-        <v>916.916091403662</v>
+        <v>916.9160914036617</v>
       </c>
       <c r="J14" s="168" t="n">
-        <v>979.0124015109074</v>
+        <v>979.012401510907</v>
       </c>
       <c r="K14" s="168" t="n">
         <v>1038.248132685951</v>
       </c>
       <c r="L14" s="169" t="n">
-        <v>1100.619507603406</v>
+        <v>1100.619507603405</v>
       </c>
       <c r="M14" s="170" t="n">
         <v>135310293.6701245</v>
@@ -2782,7 +2782,7 @@
         <v>154371309.1828507</v>
       </c>
       <c r="O14" s="171" t="n">
-        <v>177899212.7774968</v>
+        <v>177899212.7774967</v>
       </c>
       <c r="P14" s="171" t="n">
         <v>203720343.9611197</v>
@@ -2796,22 +2796,22 @@
         </is>
       </c>
       <c r="T14" s="167" t="n">
-        <v>987.4144795212831</v>
+        <v>987.4144795212826</v>
       </c>
       <c r="U14" s="168" t="n">
         <v>1031.732975576244</v>
       </c>
       <c r="V14" s="168" t="n">
-        <v>1098.02075647907</v>
+        <v>1098.020756479069</v>
       </c>
       <c r="W14" s="168" t="n">
         <v>1159.512347055807</v>
       </c>
       <c r="X14" s="169" t="n">
-        <v>1224.900565533283</v>
+        <v>1224.900565533282</v>
       </c>
       <c r="Y14" s="167" t="n">
-        <v>979.741267928969</v>
+        <v>979.7412679289686</v>
       </c>
       <c r="Z14" s="168" t="n">
         <v>1025.894246735829</v>
@@ -2832,7 +2832,7 @@
         <v>154371309.1828507</v>
       </c>
       <c r="AF14" s="171" t="n">
-        <v>177899212.7774968</v>
+        <v>177899212.7774967</v>
       </c>
       <c r="AG14" s="171" t="n">
         <v>203720343.9611197</v>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="T19" s="74" t="n">
-        <v>90770.18477882954</v>
+        <v>90770.18477882956</v>
       </c>
       <c r="U19" s="75" t="n">
-        <v>99350.30131074588</v>
+        <v>99350.3013107459</v>
       </c>
       <c r="V19" s="75" t="n">
         <v>107413.1502734667</v>
@@ -3232,10 +3232,10 @@
         <v>30.33146387675285</v>
       </c>
       <c r="AD19" s="74" t="n">
-        <v>91572.11847410812</v>
+        <v>91572.11847410814</v>
       </c>
       <c r="AE19" s="75" t="n">
-        <v>99985.81090161098</v>
+        <v>99985.810901611</v>
       </c>
       <c r="AF19" s="75" t="n">
         <v>107869.4930351635</v>
@@ -3289,19 +3289,19 @@
         </is>
       </c>
       <c r="C20" s="79" t="n">
-        <v>24363.46566804107</v>
+        <v>24363.46566804108</v>
       </c>
       <c r="D20" s="80" t="n">
-        <v>25902.71885808726</v>
+        <v>25902.71885808727</v>
       </c>
       <c r="E20" s="80" t="n">
         <v>27594.28627823325</v>
       </c>
       <c r="F20" s="80" t="n">
-        <v>29509.54823003766</v>
+        <v>29509.54823003767</v>
       </c>
       <c r="G20" s="81" t="n">
-        <v>32225.47504670375</v>
+        <v>32225.47504670376</v>
       </c>
       <c r="H20" s="79" t="n">
         <v>234.6275246081198</v>
@@ -3319,19 +3319,19 @@
         <v>34.93811261153121</v>
       </c>
       <c r="M20" s="79" t="n">
-        <v>24598.09319264919</v>
+        <v>24598.0931926492</v>
       </c>
       <c r="N20" s="80" t="n">
         <v>26094.00600724539</v>
       </c>
       <c r="O20" s="80" t="n">
-        <v>27739.06644940479</v>
+        <v>27739.0664494048</v>
       </c>
       <c r="P20" s="80" t="n">
         <v>29603.54742399331</v>
       </c>
       <c r="Q20" s="81" t="n">
-        <v>32260.41315931528</v>
+        <v>32260.41315931529</v>
       </c>
       <c r="S20" s="32" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
         <v>24084.48333297903</v>
       </c>
       <c r="U20" s="80" t="n">
-        <v>25606.11076915827</v>
+        <v>25606.11076915828</v>
       </c>
       <c r="V20" s="80" t="n">
         <v>27278.30830838431</v>
@@ -3369,10 +3369,10 @@
         <v>34.81840391551756</v>
       </c>
       <c r="AD20" s="79" t="n">
-        <v>24318.30695168267</v>
+        <v>24318.30695168268</v>
       </c>
       <c r="AE20" s="80" t="n">
-        <v>25796.74250983899</v>
+        <v>25796.742509839</v>
       </c>
       <c r="AF20" s="80" t="n">
         <v>27422.59241825763</v>
@@ -3381,7 +3381,7 @@
         <v>29265.31601112272</v>
       </c>
       <c r="AH20" s="81" t="n">
-        <v>31891.2844434645</v>
+        <v>31891.28444346451</v>
       </c>
       <c r="AS20" s="82" t="inlineStr">
         <is>
@@ -3418,7 +3418,7 @@
         <v>159330.3717431031</v>
       </c>
       <c r="F21" s="86" t="n">
-        <v>171543.4305004976</v>
+        <v>171543.4305004977</v>
       </c>
       <c r="G21" s="87" t="n">
         <v>188429.8307206147</v>
@@ -3448,7 +3448,7 @@
         <v>160041.5382581457</v>
       </c>
       <c r="P21" s="86" t="n">
-        <v>171960.7102570369</v>
+        <v>171960.710257037</v>
       </c>
       <c r="Q21" s="87" t="n">
         <v>188502.4144986588</v>
@@ -3468,7 +3468,7 @@
         <v>134691.458581851</v>
       </c>
       <c r="W21" s="86" t="n">
-        <v>144981.264521751</v>
+        <v>144981.2645217511</v>
       </c>
       <c r="X21" s="87" t="n">
         <v>159220.2166031419</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="C22" s="79" t="n">
-        <v>8372.046597771947</v>
+        <v>8372.046597771949</v>
       </c>
       <c r="D22" s="80" t="n">
         <v>9151.95398242366</v>
@@ -3596,7 +3596,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="79" t="n">
-        <v>8409.760077670009</v>
+        <v>8409.760077670011</v>
       </c>
       <c r="N22" s="80" t="n">
         <v>9175.941637259844</v>
@@ -3616,7 +3616,7 @@
         </is>
       </c>
       <c r="T22" s="79" t="n">
-        <v>6819.596772554498</v>
+        <v>6819.5967725545</v>
       </c>
       <c r="U22" s="80" t="n">
         <v>7454.88395366953</v>
@@ -3625,7 +3625,7 @@
         <v>8169.062008648177</v>
       </c>
       <c r="W22" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>9032.016118008522</v>
       </c>
       <c r="X22" s="81" t="n">
         <v>10195.85396456519</v>
@@ -3646,7 +3646,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="79" t="n">
-        <v>6852.891465129731</v>
+        <v>6852.891465129733</v>
       </c>
       <c r="AE22" s="80" t="n">
         <v>7476.061039303906</v>
@@ -3655,7 +3655,7 @@
         <v>8176.473725753166</v>
       </c>
       <c r="AG22" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>9032.016118008522</v>
       </c>
       <c r="AH22" s="81" t="n">
         <v>10195.85396456519</v>
@@ -3706,7 +3706,7 @@
         <v>144059.9524227434</v>
       </c>
       <c r="D23" s="86" t="n">
-        <v>156902.135196021</v>
+        <v>156902.1351960211</v>
       </c>
       <c r="E23" s="86" t="n">
         <v>169359.0831284644</v>
@@ -3762,7 +3762,7 @@
         <v>142860.5205904992</v>
       </c>
       <c r="W23" s="86" t="n">
-        <v>154013.2806397595</v>
+        <v>154013.2806397596</v>
       </c>
       <c r="X23" s="87" t="n">
         <v>169416.0705677071</v>
@@ -3771,7 +3771,7 @@
         <v>1069.052006557457</v>
       </c>
       <c r="Z23" s="86" t="n">
-        <v>847.3184171802002</v>
+        <v>847.3184171802003</v>
       </c>
       <c r="AA23" s="86" t="n">
         <v>608.0385886751235</v>
@@ -3792,7 +3792,7 @@
         <v>143468.5591791743</v>
       </c>
       <c r="AG23" s="86" t="n">
-        <v>154367.427929142</v>
+        <v>154367.4279291421</v>
       </c>
       <c r="AH23" s="87" t="n">
         <v>169481.2204354994</v>
@@ -3945,7 +3945,7 @@
         <v>153385.3511541392</v>
       </c>
       <c r="D25" s="92" t="n">
-        <v>167351.4706917583</v>
+        <v>167351.4706917584</v>
       </c>
       <c r="E25" s="92" t="n">
         <v>180989.5451735538</v>
@@ -3981,7 +3981,7 @@
         <v>181712.930809605</v>
       </c>
       <c r="P25" s="92" t="n">
-        <v>196215.4686800105</v>
+        <v>196215.4686800106</v>
       </c>
       <c r="Q25" s="93" t="n">
         <v>215998.0465161036</v>
@@ -3992,7 +3992,7 @@
         </is>
       </c>
       <c r="T25" s="91" t="n">
-        <v>137034.9498376056</v>
+        <v>137034.9498376057</v>
       </c>
       <c r="U25" s="92" t="n">
         <v>149623.3161459545</v>
@@ -4001,7 +4001,7 @@
         <v>162018.0781900254</v>
       </c>
       <c r="W25" s="92" t="n">
-        <v>175694.8466123704</v>
+        <v>175694.8466123705</v>
       </c>
       <c r="X25" s="93" t="n">
         <v>194082.4180257854</v>
@@ -4010,7 +4010,7 @@
         <v>1073.240660637687</v>
       </c>
       <c r="Z25" s="92" t="n">
-        <v>851.5594798971542</v>
+        <v>851.5594798971543</v>
       </c>
       <c r="AA25" s="92" t="n">
         <v>612.3622712061436</v>
@@ -4031,7 +4031,7 @@
         <v>162630.4404612315</v>
       </c>
       <c r="AG25" s="92" t="n">
-        <v>176053.3697572503</v>
+        <v>176053.3697572504</v>
       </c>
       <c r="AH25" s="93" t="n">
         <v>194151.9966484447</v>
@@ -4408,43 +4408,43 @@
         </is>
       </c>
       <c r="C35" s="148" t="n">
-        <v>454.9781866303243</v>
+        <v>454.9781866303242</v>
       </c>
       <c r="D35" s="149" t="n">
-        <v>491.5070694451438</v>
+        <v>491.5070694451437</v>
       </c>
       <c r="E35" s="149" t="n">
-        <v>527.2984719396594</v>
+        <v>527.2984719396593</v>
       </c>
       <c r="F35" s="149" t="n">
-        <v>563.8309448169134</v>
+        <v>563.8309448169133</v>
       </c>
       <c r="G35" s="150" t="n">
         <v>596.3012348905719</v>
       </c>
       <c r="H35" s="148" t="n">
-        <v>450.9464282190903</v>
+        <v>450.9464282190902</v>
       </c>
       <c r="I35" s="149" t="n">
-        <v>488.3458493907415</v>
+        <v>488.3458493907414</v>
       </c>
       <c r="J35" s="149" t="n">
-        <v>525.0411093252825</v>
+        <v>525.0411093252824</v>
       </c>
       <c r="K35" s="149" t="n">
-        <v>562.5505344644238</v>
+        <v>562.5505344644237</v>
       </c>
       <c r="L35" s="150" t="n">
         <v>596.1575593321863</v>
       </c>
       <c r="M35" s="151" t="n">
-        <v>50650191.91023623</v>
+        <v>50650191.91023622</v>
       </c>
       <c r="N35" s="152" t="n">
-        <v>59888889.14168425</v>
+        <v>59888889.14168424</v>
       </c>
       <c r="O35" s="152" t="n">
-        <v>69464236.56493822</v>
+        <v>69464236.5649382</v>
       </c>
       <c r="P35" s="152" t="n">
         <v>80083098.03656769</v>
@@ -4458,43 +4458,43 @@
         </is>
       </c>
       <c r="T35" s="148" t="n">
-        <v>558.0047240583501</v>
+        <v>558.00472405835</v>
       </c>
       <c r="U35" s="149" t="n">
-        <v>602.8053096121469</v>
+        <v>602.8053096121466</v>
       </c>
       <c r="V35" s="149" t="n">
-        <v>646.7014177322507</v>
+        <v>646.7014177322505</v>
       </c>
       <c r="W35" s="149" t="n">
-        <v>691.5064062922949</v>
+        <v>691.5064062922947</v>
       </c>
       <c r="X35" s="150" t="n">
         <v>731.3293599746171</v>
       </c>
       <c r="Y35" s="148" t="n">
-        <v>553.1180533358252</v>
+        <v>553.1180533358249</v>
       </c>
       <c r="Z35" s="149" t="n">
-        <v>598.9738804100584</v>
+        <v>598.9738804100582</v>
       </c>
       <c r="AA35" s="149" t="n">
-        <v>643.9655421602298</v>
+        <v>643.9655421602297</v>
       </c>
       <c r="AB35" s="149" t="n">
-        <v>689.9546130689093</v>
+        <v>689.9546130689092</v>
       </c>
       <c r="AC35" s="150" t="n">
         <v>731.1552365796285</v>
       </c>
       <c r="AD35" s="151" t="n">
-        <v>50650191.91023623</v>
+        <v>50650191.91023622</v>
       </c>
       <c r="AE35" s="152" t="n">
-        <v>59888889.14168425</v>
+        <v>59888889.14168424</v>
       </c>
       <c r="AF35" s="152" t="n">
-        <v>69464236.56493822</v>
+        <v>69464236.5649382</v>
       </c>
       <c r="AG35" s="152" t="n">
         <v>80083098.03656769</v>
@@ -4510,34 +4510,34 @@
         </is>
       </c>
       <c r="C36" s="155" t="n">
-        <v>875.6653356440744</v>
+        <v>875.6653356440743</v>
       </c>
       <c r="D36" s="156" t="n">
-        <v>936.067405281334</v>
+        <v>936.0674052813339</v>
       </c>
       <c r="E36" s="156" t="n">
-        <v>994.6655828011826</v>
+        <v>994.6655828011825</v>
       </c>
       <c r="F36" s="156" t="n">
-        <v>1050.816358260222</v>
+        <v>1050.816358260223</v>
       </c>
       <c r="G36" s="157" t="n">
         <v>1098.550016726195</v>
       </c>
       <c r="H36" s="155" t="n">
-        <v>867.3128512267576</v>
+        <v>867.3128512267575</v>
       </c>
       <c r="I36" s="156" t="n">
-        <v>929.205382434923</v>
+        <v>929.2053824349229</v>
       </c>
       <c r="J36" s="156" t="n">
-        <v>989.4740651414567</v>
+        <v>989.4740651414564</v>
       </c>
       <c r="K36" s="156" t="n">
         <v>1047.479734805703</v>
       </c>
       <c r="L36" s="157" t="n">
-        <v>1097.360284158164</v>
+        <v>1097.360284158163</v>
       </c>
       <c r="M36" s="158" t="n">
         <v>21334242.34165807</v>
@@ -4549,7 +4549,7 @@
         <v>27447086.84292155</v>
       </c>
       <c r="P36" s="159" t="n">
-        <v>31009116.00499257</v>
+        <v>31009116.00499258</v>
       </c>
       <c r="Q36" s="160" t="n">
         <v>35401296.15156598</v>
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="T36" s="155" t="n">
-        <v>885.8085949655795</v>
+        <v>885.8085949655793</v>
       </c>
       <c r="U36" s="156" t="n">
-        <v>946.9103312802183</v>
+        <v>946.9103312802182</v>
       </c>
       <c r="V36" s="156" t="n">
         <v>1006.187280113898</v>
@@ -4575,10 +4575,10 @@
         <v>1111.275058181789</v>
       </c>
       <c r="Y36" s="155" t="n">
-        <v>877.2914325017135</v>
+        <v>877.2914325017134</v>
       </c>
       <c r="Z36" s="156" t="n">
-        <v>939.9128910161362</v>
+        <v>939.912891016136</v>
       </c>
       <c r="AA36" s="156" t="n">
         <v>1000.893220607677</v>
@@ -4587,7 +4587,7 @@
         <v>1059.585893185199</v>
       </c>
       <c r="AC36" s="157" t="n">
-        <v>1110.061785511458</v>
+        <v>1110.061785511457</v>
       </c>
       <c r="AD36" s="158" t="n">
         <v>21334242.34165807</v>
@@ -4599,7 +4599,7 @@
         <v>27447086.84292155</v>
       </c>
       <c r="AG36" s="159" t="n">
-        <v>31009116.00499257</v>
+        <v>31009116.00499258</v>
       </c>
       <c r="AH36" s="160" t="n">
         <v>35401296.15156598</v>
@@ -4621,7 +4621,7 @@
         <v>608.241368846582</v>
       </c>
       <c r="F37" s="162" t="n">
-        <v>647.6040132661215</v>
+        <v>647.6040132661213</v>
       </c>
       <c r="G37" s="163" t="n">
         <v>682.1963690335253</v>
@@ -4630,16 +4630,16 @@
         <v>525.7490947903354</v>
       </c>
       <c r="I37" s="162" t="n">
-        <v>565.6925434251127</v>
+        <v>565.6925434251126</v>
       </c>
       <c r="J37" s="162" t="n">
-        <v>605.5385649414505</v>
+        <v>605.5385649414503</v>
       </c>
       <c r="K37" s="162" t="n">
-        <v>646.0325377553166</v>
+        <v>646.0325377553164</v>
       </c>
       <c r="L37" s="163" t="n">
-        <v>681.9336859800267</v>
+        <v>681.9336859800264</v>
       </c>
       <c r="M37" s="164" t="n">
         <v>71984434.2518943</v>
@@ -4648,7 +4648,7 @@
         <v>84135579.97290587</v>
       </c>
       <c r="O37" s="165" t="n">
-        <v>96911323.40785977</v>
+        <v>96911323.40785976</v>
       </c>
       <c r="P37" s="165" t="n">
         <v>111092214.0415603</v>
@@ -4662,34 +4662,34 @@
         </is>
       </c>
       <c r="T37" s="161" t="n">
-        <v>626.7436529599214</v>
+        <v>626.7436529599212</v>
       </c>
       <c r="U37" s="162" t="n">
-        <v>673.3194285308452</v>
+        <v>673.3194285308451</v>
       </c>
       <c r="V37" s="162" t="n">
-        <v>719.5060802535407</v>
+        <v>719.5060802535406</v>
       </c>
       <c r="W37" s="162" t="n">
-        <v>766.2522078836848</v>
+        <v>766.2522078836846</v>
       </c>
       <c r="X37" s="163" t="n">
-        <v>807.3481438328138</v>
+        <v>807.3481438328137</v>
       </c>
       <c r="Y37" s="161" t="n">
-        <v>621.1422038310557</v>
+        <v>621.1422038310554</v>
       </c>
       <c r="Z37" s="162" t="n">
-        <v>668.897058383671</v>
+        <v>668.8970583836709</v>
       </c>
       <c r="AA37" s="162" t="n">
-        <v>716.3118454643435</v>
+        <v>716.3118454643434</v>
       </c>
       <c r="AB37" s="162" t="n">
-        <v>764.3850363593905</v>
+        <v>764.3850363593903</v>
       </c>
       <c r="AC37" s="163" t="n">
-        <v>807.0179275298451</v>
+        <v>807.017927529845</v>
       </c>
       <c r="AD37" s="164" t="n">
         <v>71984434.2518943</v>
@@ -4698,7 +4698,7 @@
         <v>84135579.97290587</v>
       </c>
       <c r="AF37" s="165" t="n">
-        <v>96911323.40785977</v>
+        <v>96911323.40785976</v>
       </c>
       <c r="AG37" s="165" t="n">
         <v>111092214.0415603</v>
@@ -4714,40 +4714,40 @@
         </is>
       </c>
       <c r="C38" s="155" t="n">
-        <v>863.3906662027556</v>
+        <v>863.3906662027555</v>
       </c>
       <c r="D38" s="156" t="n">
-        <v>914.8649995349315</v>
+        <v>914.8649995349317</v>
       </c>
       <c r="E38" s="156" t="n">
         <v>955.9974705078605</v>
       </c>
       <c r="F38" s="156" t="n">
-        <v>993.6907271849803</v>
+        <v>993.6907271849805</v>
       </c>
       <c r="G38" s="157" t="n">
-        <v>1019.451521753969</v>
+        <v>1019.45152175397</v>
       </c>
       <c r="H38" s="155" t="n">
         <v>859.518799914861</v>
       </c>
       <c r="I38" s="156" t="n">
-        <v>912.47336860504</v>
+        <v>912.4733686050402</v>
       </c>
       <c r="J38" s="156" t="n">
         <v>955.1978413312761</v>
       </c>
       <c r="K38" s="156" t="n">
-        <v>993.6907271849803</v>
+        <v>993.6907271849805</v>
       </c>
       <c r="L38" s="157" t="n">
-        <v>1019.451521753969</v>
+        <v>1019.45152175397</v>
       </c>
       <c r="M38" s="158" t="n">
-        <v>7228346.889530835</v>
+        <v>7228346.889530836</v>
       </c>
       <c r="N38" s="159" t="n">
-        <v>8372802.375873736</v>
+        <v>8372802.375873738</v>
       </c>
       <c r="O38" s="159" t="n">
         <v>9587422.716858864</v>
@@ -4764,7 +4764,7 @@
         </is>
       </c>
       <c r="T38" s="155" t="n">
-        <v>1059.937578512172</v>
+        <v>1059.937578512171</v>
       </c>
       <c r="U38" s="156" t="n">
         <v>1123.129806970688</v>
@@ -4794,10 +4794,10 @@
         <v>1251.524969722915</v>
       </c>
       <c r="AD38" s="158" t="n">
-        <v>7228346.889530835</v>
+        <v>7228346.889530836</v>
       </c>
       <c r="AE38" s="159" t="n">
-        <v>8372802.375873736</v>
+        <v>8372802.375873738</v>
       </c>
       <c r="AF38" s="159" t="n">
         <v>9587422.716858864</v>
@@ -4816,16 +4816,16 @@
         </is>
       </c>
       <c r="C39" s="161" t="n">
-        <v>549.8598313358839</v>
+        <v>549.8598313358838</v>
       </c>
       <c r="D39" s="162" t="n">
-        <v>589.5928836991734</v>
+        <v>589.5928836991733</v>
       </c>
       <c r="E39" s="162" t="n">
-        <v>628.8339790074078</v>
+        <v>628.8339790074077</v>
       </c>
       <c r="F39" s="162" t="n">
-        <v>668.6159837445774</v>
+        <v>668.6159837445773</v>
       </c>
       <c r="G39" s="163" t="n">
         <v>703.2038612016398</v>
@@ -4834,13 +4834,13 @@
         <v>545.063547102064</v>
       </c>
       <c r="I39" s="162" t="n">
-        <v>585.8440084077572</v>
+        <v>585.8440084077571</v>
       </c>
       <c r="J39" s="162" t="n">
-        <v>626.173533479752</v>
+        <v>626.1735334797519</v>
       </c>
       <c r="K39" s="162" t="n">
-        <v>667.0918006883309</v>
+        <v>667.0918006883307</v>
       </c>
       <c r="L39" s="163" t="n">
         <v>702.9499493084761</v>
@@ -4866,31 +4866,31 @@
         </is>
       </c>
       <c r="T39" s="161" t="n">
-        <v>651.0232974631691</v>
+        <v>651.023297463169</v>
       </c>
       <c r="U39" s="162" t="n">
         <v>698.6441876176754</v>
       </c>
       <c r="V39" s="162" t="n">
-        <v>745.4735967957912</v>
+        <v>745.4735967957911</v>
       </c>
       <c r="W39" s="162" t="n">
-        <v>792.8561006629263</v>
+        <v>792.856100662926</v>
       </c>
       <c r="X39" s="163" t="n">
         <v>834.0797404047554</v>
       </c>
       <c r="Y39" s="161" t="n">
-        <v>645.3531088117809</v>
+        <v>645.3531088117808</v>
       </c>
       <c r="Z39" s="162" t="n">
         <v>694.2018925385596</v>
       </c>
       <c r="AA39" s="162" t="n">
-        <v>742.3141818251272</v>
+        <v>742.3141818251271</v>
       </c>
       <c r="AB39" s="162" t="n">
-        <v>791.0371428511203</v>
+        <v>791.0371428511199</v>
       </c>
       <c r="AC39" s="163" t="n">
         <v>833.7591138204298</v>
@@ -4918,49 +4918,49 @@
         </is>
       </c>
       <c r="C40" s="155" t="n">
-        <v>6427.932072436402</v>
+        <v>6427.932072436399</v>
       </c>
       <c r="D40" s="156" t="n">
-        <v>6697.206360277312</v>
+        <v>6697.206360277311</v>
       </c>
       <c r="E40" s="156" t="n">
-        <v>7046.892393719898</v>
+        <v>7046.892393719897</v>
       </c>
       <c r="F40" s="156" t="n">
-        <v>7326.464733788702</v>
+        <v>7326.464733788699</v>
       </c>
       <c r="G40" s="157" t="n">
-        <v>7637.137634855172</v>
+        <v>7637.137634855169</v>
       </c>
       <c r="H40" s="155" t="n">
-        <v>6425.379721480364</v>
+        <v>6425.37972148036</v>
       </c>
       <c r="I40" s="156" t="n">
-        <v>6694.803334925235</v>
+        <v>6694.803334925234</v>
       </c>
       <c r="J40" s="156" t="n">
         <v>7044.576352856699</v>
       </c>
       <c r="K40" s="156" t="n">
-        <v>7324.311372986042</v>
+        <v>7324.311372986039</v>
       </c>
       <c r="L40" s="157" t="n">
-        <v>7635.140664953097</v>
+        <v>7635.140664953095</v>
       </c>
       <c r="M40" s="158" t="n">
-        <v>59943029.59379704</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="N40" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="O40" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="P40" s="159" t="n">
-        <v>96436610.61872099</v>
+        <v>96436610.61872096</v>
       </c>
       <c r="Q40" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
       <c r="S40" s="32" t="inlineStr">
         <is>
@@ -4968,49 +4968,49 @@
         </is>
       </c>
       <c r="T40" s="155" t="n">
-        <v>3902.366969719231</v>
+        <v>3902.366969719229</v>
       </c>
       <c r="U40" s="156" t="n">
-        <v>4065.842108352229</v>
+        <v>4065.842108352228</v>
       </c>
       <c r="V40" s="156" t="n">
-        <v>4278.134835048896</v>
+        <v>4278.134835048895</v>
       </c>
       <c r="W40" s="156" t="n">
-        <v>4447.86187217953</v>
+        <v>4447.861872179529</v>
       </c>
       <c r="X40" s="157" t="n">
-        <v>4636.469911879788</v>
+        <v>4636.469911879786</v>
       </c>
       <c r="Y40" s="155" t="n">
-        <v>3901.303136345263</v>
+        <v>3901.303136345261</v>
       </c>
       <c r="Z40" s="156" t="n">
-        <v>4064.840526696178</v>
+        <v>4064.840526696177</v>
       </c>
       <c r="AA40" s="156" t="n">
-        <v>4277.169517678468</v>
+        <v>4277.169517678467</v>
       </c>
       <c r="AB40" s="156" t="n">
-        <v>4446.96436904227</v>
+        <v>4446.964369042269</v>
       </c>
       <c r="AC40" s="157" t="n">
-        <v>4635.637599652919</v>
+        <v>4635.637599652917</v>
       </c>
       <c r="AD40" s="158" t="n">
-        <v>59943029.59379704</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="AE40" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="AF40" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="AG40" s="159" t="n">
-        <v>96436610.61872099</v>
+        <v>96436610.61872096</v>
       </c>
       <c r="AH40" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
     </row>
     <row r="41" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -5020,13 +5020,13 @@
         </is>
       </c>
       <c r="C41" s="179" t="n">
-        <v>907.2301213131001</v>
+        <v>907.2301213130996</v>
       </c>
       <c r="D41" s="180" t="n">
-        <v>970.9489723624229</v>
+        <v>970.9489723624225</v>
       </c>
       <c r="E41" s="180" t="n">
-        <v>1041.261032315388</v>
+        <v>1041.261032315387</v>
       </c>
       <c r="F41" s="180" t="n">
         <v>1116.206950357702</v>
@@ -5035,10 +5035,10 @@
         <v>1184.093457238351</v>
       </c>
       <c r="H41" s="179" t="n">
-        <v>899.7722141574462</v>
+        <v>899.772214157446</v>
       </c>
       <c r="I41" s="180" t="n">
-        <v>965.1369590598991</v>
+        <v>965.1369590598988</v>
       </c>
       <c r="J41" s="180" t="n">
         <v>1037.115849741969</v>
@@ -5050,13 +5050,13 @@
         <v>1183.674084597787</v>
       </c>
       <c r="M41" s="182" t="n">
-        <v>139155810.7352222</v>
+        <v>139155810.7352221</v>
       </c>
       <c r="N41" s="183" t="n">
         <v>162489738.4915029</v>
       </c>
       <c r="O41" s="183" t="n">
-        <v>188457360.6457072</v>
+        <v>188457360.6457071</v>
       </c>
       <c r="P41" s="183" t="n">
         <v>218546979.7570657</v>
@@ -5070,7 +5070,7 @@
         </is>
       </c>
       <c r="T41" s="185" t="n">
-        <v>1015.476788221763</v>
+        <v>1015.476788221762</v>
       </c>
       <c r="U41" s="186" t="n">
         <v>1085.99209452755</v>
@@ -5079,13 +5079,13 @@
         <v>1163.187236579069</v>
       </c>
       <c r="W41" s="186" t="n">
-        <v>1243.900910988235</v>
+        <v>1243.900910988234</v>
       </c>
       <c r="X41" s="187" t="n">
         <v>1317.333597682667</v>
       </c>
       <c r="Y41" s="185" t="n">
-        <v>1007.585504039981</v>
+        <v>1007.58550403998</v>
       </c>
       <c r="Z41" s="186" t="n">
         <v>1079.846305342864</v>
@@ -5100,13 +5100,13 @@
         <v>1316.861502319797</v>
       </c>
       <c r="AD41" s="188" t="n">
-        <v>139155810.7352222</v>
+        <v>139155810.7352221</v>
       </c>
       <c r="AE41" s="189" t="n">
         <v>162489738.4915029</v>
       </c>
       <c r="AF41" s="189" t="n">
-        <v>188457360.6457072</v>
+        <v>188457360.6457071</v>
       </c>
       <c r="AG41" s="189" t="n">
         <v>218546979.7570657</v>
@@ -5383,13 +5383,13 @@
         <v>0.2142553568951812</v>
       </c>
       <c r="G46" s="150" t="n">
-        <v>0.2323794694415245</v>
+        <v>0.2323794694415246</v>
       </c>
       <c r="H46" s="148" t="n">
         <v>0.1629552614356427</v>
       </c>
       <c r="I46" s="149" t="n">
-        <v>0.1762119264753975</v>
+        <v>0.1762119264753974</v>
       </c>
       <c r="J46" s="149" t="n">
         <v>0.1936008173174764</v>
@@ -5398,7 +5398,7 @@
         <v>0.2137688018744488</v>
       </c>
       <c r="L46" s="150" t="n">
-        <v>0.232323478864823</v>
+        <v>0.2323234788648231</v>
       </c>
       <c r="M46" s="151" t="n">
         <v>18303.09488666798</v>
@@ -5421,7 +5421,7 @@
         </is>
       </c>
       <c r="T46" s="148" t="n">
-        <v>0.2016421463861207</v>
+        <v>0.2016421463861208</v>
       </c>
       <c r="U46" s="149" t="n">
         <v>0.2175128242184844</v>
@@ -5433,7 +5433,7 @@
         <v>0.2627719411951925</v>
       </c>
       <c r="X46" s="150" t="n">
-        <v>0.2850001286499067</v>
+        <v>0.2850001286499068</v>
       </c>
       <c r="Y46" s="148" t="n">
         <v>0.1998762853984114</v>
@@ -5473,7 +5473,7 @@
         </is>
       </c>
       <c r="C47" s="155" t="n">
-        <v>0.02775934099858849</v>
+        <v>0.02775934099858848</v>
       </c>
       <c r="D47" s="156" t="n">
         <v>0.02704214761686709</v>
@@ -5485,19 +5485,19 @@
         <v>0.02564219679468193</v>
       </c>
       <c r="G47" s="157" t="n">
-        <v>0.02442493278575341</v>
+        <v>0.0244249327857534</v>
       </c>
       <c r="H47" s="155" t="n">
         <v>0.0274945600900749</v>
       </c>
       <c r="I47" s="156" t="n">
-        <v>0.02684390993257641</v>
+        <v>0.0268439099325764</v>
       </c>
       <c r="J47" s="156" t="n">
-        <v>0.02622464315516051</v>
+        <v>0.0262246431551605</v>
       </c>
       <c r="K47" s="156" t="n">
-        <v>0.02556077595023278</v>
+        <v>0.02556077595023277</v>
       </c>
       <c r="L47" s="157" t="n">
         <v>0.02439848051907029</v>
@@ -5529,13 +5529,13 @@
         <v>0.0273553900220681</v>
       </c>
       <c r="V47" s="156" t="n">
-        <v>0.02666760382898585</v>
+        <v>0.02666760382898584</v>
       </c>
       <c r="W47" s="156" t="n">
         <v>0.02593922288567161</v>
       </c>
       <c r="X47" s="157" t="n">
-        <v>0.02470785871312725</v>
+        <v>0.02470785871312724</v>
       </c>
       <c r="Y47" s="155" t="n">
         <v>0.02781088966145149</v>
@@ -5575,7 +5575,7 @@
         </is>
       </c>
       <c r="C48" s="161" t="n">
-        <v>0.1398754629063015</v>
+        <v>0.1398754629063016</v>
       </c>
       <c r="D48" s="162" t="n">
         <v>0.151001031530668</v>
@@ -5593,7 +5593,7 @@
         <v>0.138618953039149</v>
       </c>
       <c r="I48" s="162" t="n">
-        <v>0.1500060232157289</v>
+        <v>0.1500060232157288</v>
       </c>
       <c r="J48" s="162" t="n">
         <v>0.1645904812030688</v>
@@ -5605,7 +5605,7 @@
         <v>0.196739073377902</v>
       </c>
       <c r="M48" s="164" t="n">
-        <v>18979.40863805453</v>
+        <v>18979.40863805454</v>
       </c>
       <c r="N48" s="165" t="n">
         <v>22310.42977209633</v>
@@ -5614,7 +5614,7 @@
         <v>26341.31379438754</v>
       </c>
       <c r="P48" s="165" t="n">
-        <v>31188.20978010233</v>
+        <v>31188.20978010234</v>
       </c>
       <c r="Q48" s="166" t="n">
         <v>37085.79035796333</v>
@@ -5640,7 +5640,7 @@
         <v>0.2329213660750133</v>
       </c>
       <c r="Y48" s="161" t="n">
-        <v>0.1637702904991732</v>
+        <v>0.1637702904991733</v>
       </c>
       <c r="Z48" s="162" t="n">
         <v>0.1773730073606966</v>
@@ -5649,13 +5649,13 @@
         <v>0.1946995916731317</v>
       </c>
       <c r="AB48" s="162" t="n">
-        <v>0.2145947047002701</v>
+        <v>0.21459470470027</v>
       </c>
       <c r="AC48" s="163" t="n">
-        <v>0.2328260980881166</v>
+        <v>0.2328260980881167</v>
       </c>
       <c r="AD48" s="164" t="n">
-        <v>18979.40863805453</v>
+        <v>18979.40863805454</v>
       </c>
       <c r="AE48" s="165" t="n">
         <v>22310.42977209633</v>
@@ -5664,7 +5664,7 @@
         <v>26341.31379438754</v>
       </c>
       <c r="AG48" s="165" t="n">
-        <v>31188.20978010233</v>
+        <v>31188.20978010234</v>
       </c>
       <c r="AH48" s="166" t="n">
         <v>37085.79035796333</v>
@@ -5727,34 +5727,34 @@
         </is>
       </c>
       <c r="T49" s="155" t="n">
-        <v>0.1943673696884233</v>
+        <v>0.1943673696884232</v>
       </c>
       <c r="U49" s="156" t="n">
-        <v>0.1938020417268022</v>
+        <v>0.1938020417268023</v>
       </c>
       <c r="V49" s="156" t="n">
-        <v>0.1941970529550973</v>
+        <v>0.1941970529550974</v>
       </c>
       <c r="W49" s="156" t="n">
         <v>0.1939036128309319</v>
       </c>
       <c r="X49" s="157" t="n">
-        <v>0.1906912133004352</v>
+        <v>0.1906912133004353</v>
       </c>
       <c r="Y49" s="155" t="n">
-        <v>0.1934230381090656</v>
+        <v>0.1934230381090655</v>
       </c>
       <c r="Z49" s="156" t="n">
-        <v>0.1932530678203308</v>
+        <v>0.1932530678203309</v>
       </c>
       <c r="AA49" s="156" t="n">
-        <v>0.1940210194145513</v>
+        <v>0.1940210194145514</v>
       </c>
       <c r="AB49" s="156" t="n">
         <v>0.1939036128309319</v>
       </c>
       <c r="AC49" s="157" t="n">
-        <v>0.1906912133004352</v>
+        <v>0.1906912133004353</v>
       </c>
       <c r="AD49" s="158" t="n">
         <v>1325.507087017078</v>
@@ -5806,10 +5806,10 @@
         <v>0.1799495333845529</v>
       </c>
       <c r="L50" s="163" t="n">
-        <v>0.1941607031045022</v>
+        <v>0.1941607031045023</v>
       </c>
       <c r="M50" s="164" t="n">
-        <v>20304.91572507161</v>
+        <v>20304.91572507162</v>
       </c>
       <c r="N50" s="165" t="n">
         <v>23755.20150315386</v>
@@ -5818,10 +5818,10 @@
         <v>27927.72156187446</v>
       </c>
       <c r="P50" s="165" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="Q50" s="166" t="n">
-        <v>39030.05012110031</v>
+        <v>39030.05012110033</v>
       </c>
       <c r="S50" s="42" t="inlineStr">
         <is>
@@ -5844,7 +5844,7 @@
         <v>0.2303798570602661</v>
       </c>
       <c r="Y50" s="161" t="n">
-        <v>0.16542583530732</v>
+        <v>0.1654258353073201</v>
       </c>
       <c r="Z50" s="162" t="n">
         <v>0.1782639088742189</v>
@@ -5856,10 +5856,10 @@
         <v>0.21338407187591</v>
       </c>
       <c r="AC50" s="163" t="n">
-        <v>0.2302912972942288</v>
+        <v>0.2302912972942289</v>
       </c>
       <c r="AD50" s="164" t="n">
-        <v>20304.91572507161</v>
+        <v>20304.91572507162</v>
       </c>
       <c r="AE50" s="165" t="n">
         <v>23755.20150315386</v>
@@ -5868,10 +5868,10 @@
         <v>27927.72156187446</v>
       </c>
       <c r="AG50" s="165" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="AH50" s="166" t="n">
-        <v>39030.05012110031</v>
+        <v>39030.05012110033</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -5989,7 +5989,7 @@
         <v>0.1419479697726</v>
       </c>
       <c r="E52" s="180" t="n">
-        <v>0.1543057171346229</v>
+        <v>0.154305717134623</v>
       </c>
       <c r="F52" s="180" t="n">
         <v>0.1682354753571241</v>
@@ -6004,16 +6004,16 @@
         <v>0.1410982819804833</v>
       </c>
       <c r="J52" s="180" t="n">
-        <v>0.1536914375737879</v>
+        <v>0.153691437573788</v>
       </c>
       <c r="K52" s="180" t="n">
         <v>0.167874380945212</v>
       </c>
       <c r="L52" s="181" t="n">
-        <v>0.1806963106871916</v>
+        <v>0.1806963106871917</v>
       </c>
       <c r="M52" s="182" t="n">
-        <v>20304.91572507161</v>
+        <v>20304.91572507162</v>
       </c>
       <c r="N52" s="183" t="n">
         <v>23755.20150315386</v>
@@ -6022,10 +6022,10 @@
         <v>27927.72156187446</v>
       </c>
       <c r="P52" s="183" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="Q52" s="184" t="n">
-        <v>39030.05012110031</v>
+        <v>39030.05012110033</v>
       </c>
       <c r="S52" s="51" t="inlineStr">
         <is>
@@ -6045,7 +6045,7 @@
         <v>0.1874815964819094</v>
       </c>
       <c r="X52" s="187" t="n">
-        <v>0.2011003908448568</v>
+        <v>0.2011003908448569</v>
       </c>
       <c r="Y52" s="185" t="n">
         <v>0.1470218069747998</v>
@@ -6060,10 +6060,10 @@
         <v>0.1870998003727495</v>
       </c>
       <c r="AC52" s="187" t="n">
-        <v>0.2010283221128695</v>
+        <v>0.2010283221128696</v>
       </c>
       <c r="AD52" s="188" t="n">
-        <v>20304.91572507161</v>
+        <v>20304.91572507162</v>
       </c>
       <c r="AE52" s="189" t="n">
         <v>23755.20150315386</v>
@@ -6072,10 +6072,10 @@
         <v>27927.72156187446</v>
       </c>
       <c r="AG52" s="189" t="n">
-        <v>32939.55033653139</v>
+        <v>32939.5503365314</v>
       </c>
       <c r="AH52" s="190" t="n">
-        <v>39030.05012110031</v>
+        <v>39030.05012110033</v>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1" thickBot="1"/>
@@ -6334,7 +6334,7 @@
         </is>
       </c>
       <c r="C57" s="148" t="n">
-        <v>0.009347875851720144</v>
+        <v>0.009347875851720143</v>
       </c>
       <c r="D57" s="149" t="n">
         <v>0.008392899637464634</v>
@@ -6349,7 +6349,7 @@
         <v>0</v>
       </c>
       <c r="H57" s="148" t="n">
-        <v>0.009265040282455884</v>
+        <v>0.009265040282455882</v>
       </c>
       <c r="I57" s="149" t="n">
         <v>0.008338919126709234</v>
@@ -6367,7 +6367,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N57" s="152" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O57" s="152" t="n">
         <v>1006.132504090373</v>
@@ -6393,13 +6393,13 @@
         <v>0.009366939723198015</v>
       </c>
       <c r="W57" s="149" t="n">
-        <v>0.0003399857890771006</v>
+        <v>0.0003399857890771005</v>
       </c>
       <c r="X57" s="150" t="n">
         <v>0</v>
       </c>
       <c r="Y57" s="148" t="n">
-        <v>0.01136423469490307</v>
+        <v>0.01136423469490306</v>
       </c>
       <c r="Z57" s="149" t="n">
         <v>0.01022798648536109</v>
@@ -6408,7 +6408,7 @@
         <v>0.009327312809029258</v>
       </c>
       <c r="AB57" s="149" t="n">
-        <v>0.0003392228349833475</v>
+        <v>0.0003392228349833474</v>
       </c>
       <c r="AC57" s="150" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE57" s="152" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF57" s="152" t="n">
         <v>1006.132504090373</v>
@@ -6547,7 +6547,7 @@
         <v>0.006314756521830092</v>
       </c>
       <c r="F59" s="162" t="n">
-        <v>0.0002295257057597095</v>
+        <v>0.0002295257057597094</v>
       </c>
       <c r="G59" s="163" t="n">
         <v>0</v>
@@ -6556,13 +6556,13 @@
         <v>0.007600521529931641</v>
       </c>
       <c r="I59" s="162" t="n">
-        <v>0.006875895696508606</v>
+        <v>0.006875895696508605</v>
       </c>
       <c r="J59" s="162" t="n">
-        <v>0.006286696035547283</v>
+        <v>0.006286696035547282</v>
       </c>
       <c r="K59" s="162" t="n">
-        <v>0.0002289687388195535</v>
+        <v>0.0002289687388195534</v>
       </c>
       <c r="L59" s="163" t="n">
         <v>0</v>
@@ -6571,7 +6571,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N59" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O59" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6588,7 +6588,7 @@
         </is>
       </c>
       <c r="T59" s="161" t="n">
-        <v>0.009060555073270386</v>
+        <v>0.009060555073270384</v>
       </c>
       <c r="U59" s="162" t="n">
         <v>0.008184081997933841</v>
@@ -6597,13 +6597,13 @@
         <v>0.007469905773415866</v>
       </c>
       <c r="W59" s="162" t="n">
-        <v>0.0002715773454173543</v>
+        <v>0.0002715773454173542</v>
       </c>
       <c r="X59" s="163" t="n">
         <v>0</v>
       </c>
       <c r="Y59" s="161" t="n">
-        <v>0.008979577407070621</v>
+        <v>0.008979577407070618</v>
       </c>
       <c r="Z59" s="162" t="n">
         <v>0.008130328848424016</v>
@@ -6612,7 +6612,7 @@
         <v>0.00743674325603302</v>
       </c>
       <c r="AB59" s="162" t="n">
-        <v>0.0002709155770324941</v>
+        <v>0.000270915577032494</v>
       </c>
       <c r="AC59" s="163" t="n">
         <v>0</v>
@@ -6621,7 +6621,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE59" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF59" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6742,10 +6742,10 @@
         </is>
       </c>
       <c r="C61" s="161" t="n">
-        <v>0.007223708104494293</v>
+        <v>0.007223708104494291</v>
       </c>
       <c r="D61" s="162" t="n">
-        <v>0.006517779514930913</v>
+        <v>0.006517779514930912</v>
       </c>
       <c r="E61" s="162" t="n">
         <v>0.005940823990687222</v>
@@ -6775,7 +6775,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N61" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O61" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6792,7 +6792,7 @@
         </is>
       </c>
       <c r="T61" s="161" t="n">
-        <v>0.008552729263153921</v>
+        <v>0.008552729263153919</v>
       </c>
       <c r="U61" s="162" t="n">
         <v>0.007723310270826489</v>
@@ -6801,7 +6801,7 @@
         <v>0.007042761008651153</v>
       </c>
       <c r="W61" s="162" t="n">
-        <v>0.0002556508555009887</v>
+        <v>0.0002556508555009886</v>
       </c>
       <c r="X61" s="163" t="n">
         <v>0</v>
@@ -6810,7 +6810,7 @@
         <v>0.00847823793758185</v>
       </c>
       <c r="Z61" s="162" t="n">
-        <v>0.007674201978195345</v>
+        <v>0.007674201978195346</v>
       </c>
       <c r="AA61" s="162" t="n">
         <v>0.00701291286290705</v>
@@ -6825,7 +6825,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE61" s="165" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF61" s="165" t="n">
         <v>1006.132504090373</v>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="C63" s="179" t="n">
-        <v>0.006784526931802451</v>
+        <v>0.006784526931802449</v>
       </c>
       <c r="D63" s="180" t="n">
         <v>0.006110812880235475</v>
@@ -6964,7 +6964,7 @@
         <v>0.006728754564060537</v>
       </c>
       <c r="I63" s="180" t="n">
-        <v>0.0060742341034304</v>
+        <v>0.006074234103430399</v>
       </c>
       <c r="J63" s="180" t="n">
         <v>0.005536933995878243</v>
@@ -6979,7 +6979,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="N63" s="183" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="O63" s="183" t="n">
         <v>1006.132504090373</v>
@@ -6996,31 +6996,31 @@
         </is>
       </c>
       <c r="T63" s="185" t="n">
-        <v>0.007594026539087004</v>
+        <v>0.007594026539087002</v>
       </c>
       <c r="U63" s="186" t="n">
-        <v>0.006834854011870508</v>
+        <v>0.006834854011870509</v>
       </c>
       <c r="V63" s="186" t="n">
         <v>0.006210001472245061</v>
       </c>
       <c r="W63" s="186" t="n">
-        <v>0.0002241023439972437</v>
+        <v>0.0002241023439972436</v>
       </c>
       <c r="X63" s="187" t="n">
         <v>0</v>
       </c>
       <c r="Y63" s="185" t="n">
-        <v>0.007535013253703228</v>
+        <v>0.007535013253703226</v>
       </c>
       <c r="Z63" s="186" t="n">
-        <v>0.006796174566525804</v>
+        <v>0.006796174566525805</v>
       </c>
       <c r="AA63" s="186" t="n">
         <v>0.006186618576675495</v>
       </c>
       <c r="AB63" s="186" t="n">
-        <v>0.0002236459717207253</v>
+        <v>0.0002236459717207252</v>
       </c>
       <c r="AC63" s="187" t="n">
         <v>0</v>
@@ -7029,7 +7029,7 @@
         <v>1040.647045849234</v>
       </c>
       <c r="AE63" s="189" t="n">
-        <v>1022.653522629546</v>
+        <v>1022.653522629547</v>
       </c>
       <c r="AF63" s="189" t="n">
         <v>1006.132504090373</v>
@@ -7297,7 +7297,7 @@
         </is>
       </c>
       <c r="C68" s="148" t="n">
-        <v>0.003967630335192824</v>
+        <v>0.003967630335192823</v>
       </c>
       <c r="D68" s="149" t="n">
         <v>0.005625676077348638</v>
@@ -7306,22 +7306,22 @@
         <v>0.007315384306060658</v>
       </c>
       <c r="F68" s="149" t="n">
-        <v>0.00891942391509444</v>
+        <v>0.008919423915094439</v>
       </c>
       <c r="G68" s="150" t="n">
         <v>0.01034230280537292</v>
       </c>
       <c r="H68" s="148" t="n">
-        <v>0.003932471447477668</v>
+        <v>0.003932471447477667</v>
       </c>
       <c r="I68" s="149" t="n">
-        <v>0.005589493484786212</v>
+        <v>0.005589493484786211</v>
       </c>
       <c r="J68" s="149" t="n">
         <v>0.007284067175590782</v>
       </c>
       <c r="K68" s="149" t="n">
-        <v>0.008899168689970465</v>
+        <v>0.008899168689970463</v>
       </c>
       <c r="L68" s="150" t="n">
         <v>0.01033981088343212</v>
@@ -7347,10 +7347,10 @@
         </is>
       </c>
       <c r="T68" s="148" t="n">
-        <v>0.00486607168302264</v>
+        <v>0.004866071683022639</v>
       </c>
       <c r="U68" s="149" t="n">
-        <v>0.00689956995615966</v>
+        <v>0.006899569956159659</v>
       </c>
       <c r="V68" s="149" t="n">
         <v>0.008971900458166045</v>
@@ -7362,10 +7362,10 @@
         <v>0.01268424287718451</v>
       </c>
       <c r="Y68" s="148" t="n">
-        <v>0.004823457545539731</v>
+        <v>0.00482345754553973</v>
       </c>
       <c r="Z68" s="149" t="n">
-        <v>0.006855716304922097</v>
+        <v>0.006855716304922096</v>
       </c>
       <c r="AA68" s="149" t="n">
         <v>0.008933944760799286</v>
@@ -7510,7 +7510,7 @@
         <v>0.006048439362869245</v>
       </c>
       <c r="F70" s="162" t="n">
-        <v>0.007385070955970965</v>
+        <v>0.007385070955970964</v>
       </c>
       <c r="G70" s="163" t="n">
         <v>0.008573550906029752</v>
@@ -7519,13 +7519,13 @@
         <v>0.003225979919266236</v>
       </c>
       <c r="I70" s="162" t="n">
-        <v>0.004608843617946327</v>
+        <v>0.004608843617946326</v>
       </c>
       <c r="J70" s="162" t="n">
         <v>0.006021562293391194</v>
       </c>
       <c r="K70" s="162" t="n">
-        <v>0.007367150347211403</v>
+        <v>0.007367150347211401</v>
       </c>
       <c r="L70" s="163" t="n">
         <v>0.008570249618257562</v>
@@ -7551,22 +7551,22 @@
         </is>
       </c>
       <c r="T70" s="161" t="n">
-        <v>0.003845679353537595</v>
+        <v>0.003845679353537594</v>
       </c>
       <c r="U70" s="162" t="n">
-        <v>0.005485707717189424</v>
+        <v>0.005485707717189423</v>
       </c>
       <c r="V70" s="162" t="n">
         <v>0.007154871602833972</v>
       </c>
       <c r="W70" s="162" t="n">
-        <v>0.008738097370414272</v>
+        <v>0.008738097370414271</v>
       </c>
       <c r="X70" s="163" t="n">
         <v>0.01014640464862852</v>
       </c>
       <c r="Y70" s="161" t="n">
-        <v>0.00381130903775851</v>
+        <v>0.003811309037758509</v>
       </c>
       <c r="Z70" s="162" t="n">
         <v>0.005449677522579481</v>
@@ -7575,7 +7575,7 @@
         <v>0.007123107674198431</v>
       </c>
       <c r="AB70" s="162" t="n">
-        <v>0.00871680473801637</v>
+        <v>0.008716804738016368</v>
       </c>
       <c r="AC70" s="163" t="n">
         <v>0.01014225463198813</v>
@@ -7633,7 +7633,7 @@
         <v>0.02262063825125281</v>
       </c>
       <c r="M71" s="158" t="n">
-        <v>74.0718162432468</v>
+        <v>74.07181624324681</v>
       </c>
       <c r="N71" s="159" t="n">
         <v>115.7327516516777</v>
@@ -7662,10 +7662,10 @@
         <v>0.02011988782301449</v>
       </c>
       <c r="W71" s="156" t="n">
-        <v>0.02428558399958972</v>
+        <v>0.02428558399958971</v>
       </c>
       <c r="X71" s="157" t="n">
-        <v>0.02777012246134493</v>
+        <v>0.02777012246134494</v>
       </c>
       <c r="Y71" s="155" t="n">
         <v>0.01080884129278189</v>
@@ -7677,13 +7677,13 @@
         <v>0.020101649775449</v>
       </c>
       <c r="AB71" s="156" t="n">
-        <v>0.02428558399958972</v>
+        <v>0.02428558399958971</v>
       </c>
       <c r="AC71" s="157" t="n">
-        <v>0.02777012246134493</v>
+        <v>0.02777012246134494</v>
       </c>
       <c r="AD71" s="158" t="n">
-        <v>74.0718162432468</v>
+        <v>74.07181624324681</v>
       </c>
       <c r="AE71" s="159" t="n">
         <v>115.7327516516777</v>
@@ -7708,13 +7708,13 @@
         <v>0.003580218050778806</v>
       </c>
       <c r="D72" s="162" t="n">
-        <v>0.005106413017960178</v>
+        <v>0.005106413017960177</v>
       </c>
       <c r="E72" s="162" t="n">
         <v>0.006660762933684247</v>
       </c>
       <c r="F72" s="162" t="n">
-        <v>0.008137740960250077</v>
+        <v>0.008137740960250075</v>
       </c>
       <c r="G72" s="163" t="n">
         <v>0.009448538508173822</v>
@@ -7723,7 +7723,7 @@
         <v>0.003548988740303682</v>
       </c>
       <c r="I72" s="162" t="n">
-        <v>0.005073944333008132</v>
+        <v>0.005073944333008131</v>
       </c>
       <c r="J72" s="162" t="n">
         <v>0.00663258284553814</v>
@@ -7755,7 +7755,7 @@
         </is>
       </c>
       <c r="T72" s="161" t="n">
-        <v>0.004238908223924066</v>
+        <v>0.004238908223924065</v>
       </c>
       <c r="U72" s="162" t="n">
         <v>0.006050896937883296</v>
@@ -7764,13 +7764,13 @@
         <v>0.007896238223983103</v>
       </c>
       <c r="W72" s="162" t="n">
-        <v>0.009649870363275144</v>
+        <v>0.009649870363275141</v>
       </c>
       <c r="X72" s="163" t="n">
         <v>0.01120704106009192</v>
       </c>
       <c r="Y72" s="161" t="n">
-        <v>0.004201988793545416</v>
+        <v>0.004201988793545415</v>
       </c>
       <c r="Z72" s="162" t="n">
         <v>0.006012422604069608</v>
@@ -7779,7 +7779,7 @@
         <v>0.007862772929754023</v>
       </c>
       <c r="AB72" s="162" t="n">
-        <v>0.009627731784703926</v>
+        <v>0.009627731784703922</v>
       </c>
       <c r="AC72" s="163" t="n">
         <v>0.01120273298842751</v>
@@ -7909,16 +7909,16 @@
         </is>
       </c>
       <c r="C74" s="179" t="n">
-        <v>0.003362550844506272</v>
+        <v>0.003362550844506271</v>
       </c>
       <c r="D74" s="180" t="n">
-        <v>0.004787571345497397</v>
+        <v>0.004787571345497396</v>
       </c>
       <c r="E74" s="180" t="n">
         <v>0.006232739588925477</v>
       </c>
       <c r="F74" s="180" t="n">
-        <v>0.007590660442324311</v>
+        <v>0.00759066044232431</v>
       </c>
       <c r="G74" s="181" t="n">
         <v>0.008793253353360623</v>
@@ -7927,13 +7927,13 @@
         <v>0.003334908913958158</v>
       </c>
       <c r="I74" s="180" t="n">
-        <v>0.004758913373617464</v>
+        <v>0.004758913373617463</v>
       </c>
       <c r="J74" s="180" t="n">
         <v>0.00620792751709444</v>
       </c>
       <c r="K74" s="180" t="n">
-        <v>0.007574368129049555</v>
+        <v>0.007574368129049554</v>
       </c>
       <c r="L74" s="181" t="n">
         <v>0.008790139030031325</v>
@@ -7959,7 +7959,7 @@
         </is>
       </c>
       <c r="T74" s="185" t="n">
-        <v>0.003763755470188113</v>
+        <v>0.003763755470188112</v>
       </c>
       <c r="U74" s="186" t="n">
         <v>0.005354827886110669</v>
@@ -7968,13 +7968,13 @@
         <v>0.006962560696848668</v>
       </c>
       <c r="W74" s="186" t="n">
-        <v>0.008459031218345087</v>
+        <v>0.008459031218345086</v>
       </c>
       <c r="X74" s="187" t="n">
         <v>0.009782714366426911</v>
       </c>
       <c r="Y74" s="185" t="n">
-        <v>0.00373450727431551</v>
+        <v>0.003734507274315509</v>
       </c>
       <c r="Z74" s="186" t="n">
         <v>0.005324524126558322</v>
@@ -7983,7 +7983,7 @@
         <v>0.00693634414434078</v>
       </c>
       <c r="AB74" s="186" t="n">
-        <v>0.008441804859774275</v>
+        <v>0.008441804859774272</v>
       </c>
       <c r="AC74" s="187" t="n">
         <v>0.009779208516354616</v>
@@ -8260,43 +8260,43 @@
         </is>
       </c>
       <c r="C79" s="148" t="n">
-        <v>455.1559143254328</v>
+        <v>455.1559143254327</v>
       </c>
       <c r="D79" s="149" t="n">
-        <v>491.698440623919</v>
+        <v>491.6984406239189</v>
       </c>
       <c r="E79" s="149" t="n">
-        <v>527.5078579949244</v>
+        <v>527.5078579949243</v>
       </c>
       <c r="F79" s="149" t="n">
-        <v>564.0543968106416</v>
+        <v>564.0543968106415</v>
       </c>
       <c r="G79" s="150" t="n">
         <v>596.5439566628188</v>
       </c>
       <c r="H79" s="148" t="n">
-        <v>451.1225809922559</v>
+        <v>451.1225809922558</v>
       </c>
       <c r="I79" s="149" t="n">
-        <v>488.5359897298284</v>
+        <v>488.5359897298283</v>
       </c>
       <c r="J79" s="149" t="n">
-        <v>525.2495989996961</v>
+        <v>525.249598999696</v>
       </c>
       <c r="K79" s="149" t="n">
-        <v>562.7734790183802</v>
+        <v>562.77347901838</v>
       </c>
       <c r="L79" s="150" t="n">
         <v>596.4002226219345</v>
       </c>
       <c r="M79" s="151" t="n">
-        <v>50669977.34639457</v>
+        <v>50669977.34639456</v>
       </c>
       <c r="N79" s="152" t="n">
-        <v>59912207.234186</v>
+        <v>59912207.23418599</v>
       </c>
       <c r="O79" s="152" t="n">
-        <v>69491820.26420975</v>
+        <v>69491820.26420973</v>
       </c>
       <c r="P79" s="152" t="n">
         <v>80114835.79073799</v>
@@ -8310,43 +8310,43 @@
         </is>
       </c>
       <c r="T79" s="148" t="n">
-        <v>558.2226969115127</v>
+        <v>558.2226969115126</v>
       </c>
       <c r="U79" s="149" t="n">
-        <v>603.0400154177066</v>
+        <v>603.0400154177065</v>
       </c>
       <c r="V79" s="149" t="n">
-        <v>646.9582177534893</v>
+        <v>646.9582177534892</v>
       </c>
       <c r="W79" s="149" t="n">
-        <v>691.780457382577</v>
+        <v>691.7804573825769</v>
       </c>
       <c r="X79" s="150" t="n">
         <v>731.6270443461442</v>
       </c>
       <c r="Y79" s="148" t="n">
-        <v>553.334117313464</v>
+        <v>553.3341173134638</v>
       </c>
       <c r="Z79" s="149" t="n">
-        <v>599.2070944260421</v>
+        <v>599.207094426042</v>
       </c>
       <c r="AA79" s="149" t="n">
-        <v>644.2212557869041</v>
+        <v>644.221255786904</v>
       </c>
       <c r="AB79" s="149" t="n">
-        <v>690.2280491676008</v>
+        <v>690.2280491676006</v>
       </c>
       <c r="AC79" s="150" t="n">
         <v>731.4528500750001</v>
       </c>
       <c r="AD79" s="151" t="n">
-        <v>50669977.34639457</v>
+        <v>50669977.34639456</v>
       </c>
       <c r="AE79" s="152" t="n">
-        <v>59912207.234186</v>
+        <v>59912207.23418599</v>
       </c>
       <c r="AF79" s="152" t="n">
-        <v>69491820.26420975</v>
+        <v>69491820.26420973</v>
       </c>
       <c r="AG79" s="152" t="n">
         <v>80114835.79073799</v>
@@ -8362,31 +8362,31 @@
         </is>
       </c>
       <c r="C80" s="155" t="n">
-        <v>875.693094985073</v>
+        <v>875.6930949850729</v>
       </c>
       <c r="D80" s="156" t="n">
-        <v>936.0944474289508</v>
+        <v>936.0944474289507</v>
       </c>
       <c r="E80" s="156" t="n">
-        <v>994.6919450383414</v>
+        <v>994.6919450383413</v>
       </c>
       <c r="F80" s="156" t="n">
         <v>1050.842000457017</v>
       </c>
       <c r="G80" s="157" t="n">
-        <v>1098.574441658981</v>
+        <v>1098.57444165898</v>
       </c>
       <c r="H80" s="155" t="n">
-        <v>867.3403457868478</v>
+        <v>867.3403457868477</v>
       </c>
       <c r="I80" s="156" t="n">
-        <v>929.2322263448555</v>
+        <v>929.2322263448553</v>
       </c>
       <c r="J80" s="156" t="n">
-        <v>989.5002897846118</v>
+        <v>989.5002897846117</v>
       </c>
       <c r="K80" s="156" t="n">
-        <v>1047.505295581653</v>
+        <v>1047.505295581654</v>
       </c>
       <c r="L80" s="157" t="n">
         <v>1097.384682638683</v>
@@ -8401,10 +8401,10 @@
         <v>27447814.29004065</v>
       </c>
       <c r="P80" s="159" t="n">
-        <v>31009872.69463561</v>
+        <v>31009872.69463562</v>
       </c>
       <c r="Q80" s="160" t="n">
-        <v>35402083.25662799</v>
+        <v>35402083.25662798</v>
       </c>
       <c r="S80" s="32" t="inlineStr">
         <is>
@@ -8412,10 +8412,10 @@
         </is>
       </c>
       <c r="T80" s="155" t="n">
-        <v>885.8366758565845</v>
+        <v>885.8366758565844</v>
       </c>
       <c r="U80" s="156" t="n">
-        <v>946.9376866702403</v>
+        <v>946.9376866702402</v>
       </c>
       <c r="V80" s="156" t="n">
         <v>1006.213947717727</v>
@@ -8427,10 +8427,10 @@
         <v>1111.299766040502</v>
       </c>
       <c r="Y80" s="155" t="n">
-        <v>877.319243391375</v>
+        <v>877.3192433913749</v>
       </c>
       <c r="Z80" s="156" t="n">
-        <v>939.9400442563862</v>
+        <v>939.940044256386</v>
       </c>
       <c r="AA80" s="156" t="n">
         <v>1000.919747899773</v>
@@ -8439,7 +8439,7 @@
         <v>1059.611749377654</v>
       </c>
       <c r="AC80" s="157" t="n">
-        <v>1110.086466394519</v>
+        <v>1110.086466394518</v>
       </c>
       <c r="AD80" s="158" t="n">
         <v>21334918.65540946</v>
@@ -8451,10 +8451,10 @@
         <v>27447814.29004065</v>
       </c>
       <c r="AG80" s="159" t="n">
-        <v>31009872.69463561</v>
+        <v>31009872.69463562</v>
       </c>
       <c r="AH80" s="160" t="n">
-        <v>35402083.25662799</v>
+        <v>35402083.25662798</v>
       </c>
     </row>
     <row r="81" ht="15" customHeight="1" thickTop="1">
@@ -8467,40 +8467,40 @@
         <v>530.6655413687764</v>
       </c>
       <c r="D81" s="162" t="n">
-        <v>569.6074132652874</v>
+        <v>569.6074132652873</v>
       </c>
       <c r="E81" s="162" t="n">
-        <v>608.4190571685315</v>
+        <v>608.4190571685314</v>
       </c>
       <c r="F81" s="162" t="n">
         <v>647.7934372721503</v>
       </c>
       <c r="G81" s="163" t="n">
-        <v>682.4017574423344</v>
+        <v>682.4017574423343</v>
       </c>
       <c r="H81" s="161" t="n">
         <v>525.8985402448238</v>
       </c>
       <c r="I81" s="162" t="n">
-        <v>565.8540341876429</v>
+        <v>565.8540341876427</v>
       </c>
       <c r="J81" s="162" t="n">
-        <v>605.7154636809825</v>
+        <v>605.7154636809822</v>
       </c>
       <c r="K81" s="162" t="n">
-        <v>646.2215021051659</v>
+        <v>646.2215021051658</v>
       </c>
       <c r="L81" s="163" t="n">
-        <v>682.1389953030229</v>
+        <v>682.1389953030226</v>
       </c>
       <c r="M81" s="164" t="n">
         <v>72004896.00180402</v>
       </c>
       <c r="N81" s="165" t="n">
-        <v>84159598.53055467</v>
+        <v>84159598.53055465</v>
       </c>
       <c r="O81" s="165" t="n">
-        <v>96939634.55425039</v>
+        <v>96939634.55425037</v>
       </c>
       <c r="P81" s="165" t="n">
         <v>111124708.4853736</v>
@@ -8514,43 +8514,43 @@
         </is>
       </c>
       <c r="T81" s="161" t="n">
-        <v>626.921806362357</v>
+        <v>626.9218063623567</v>
       </c>
       <c r="U81" s="162" t="n">
-        <v>673.511644018222</v>
+        <v>673.5116440182219</v>
       </c>
       <c r="V81" s="162" t="n">
-        <v>719.7162728425044</v>
+        <v>719.7162728425043</v>
       </c>
       <c r="W81" s="162" t="n">
         <v>766.4763364558869</v>
       </c>
       <c r="X81" s="163" t="n">
-        <v>807.5912116035374</v>
+        <v>807.5912116035373</v>
       </c>
       <c r="Y81" s="161" t="n">
-        <v>621.3187650079997</v>
+        <v>621.3187650079996</v>
       </c>
       <c r="Z81" s="162" t="n">
-        <v>669.0880113974029</v>
+        <v>669.0880113974026</v>
       </c>
       <c r="AA81" s="162" t="n">
-        <v>716.5211049069467</v>
+        <v>716.5211049069466</v>
       </c>
       <c r="AB81" s="162" t="n">
-        <v>764.6086187844057</v>
+        <v>764.6086187844056</v>
       </c>
       <c r="AC81" s="163" t="n">
-        <v>807.2608958825653</v>
+        <v>807.2608958825651</v>
       </c>
       <c r="AD81" s="164" t="n">
         <v>72004896.00180402</v>
       </c>
       <c r="AE81" s="165" t="n">
-        <v>84159598.53055467</v>
+        <v>84159598.53055465</v>
       </c>
       <c r="AF81" s="165" t="n">
-        <v>96939634.55425039</v>
+        <v>96939634.55425037</v>
       </c>
       <c r="AG81" s="165" t="n">
         <v>111124708.4853736</v>
@@ -8566,46 +8566,46 @@
         </is>
       </c>
       <c r="C82" s="155" t="n">
-        <v>863.5578390543296</v>
+        <v>863.5578390543295</v>
       </c>
       <c r="D82" s="156" t="n">
-        <v>915.0355100604112</v>
+        <v>915.0355100604114</v>
       </c>
       <c r="E82" s="156" t="n">
         <v>956.1720461149794</v>
       </c>
       <c r="F82" s="156" t="n">
-        <v>993.868457005895</v>
+        <v>993.8684570058952</v>
       </c>
       <c r="G82" s="157" t="n">
         <v>1019.629473250404</v>
       </c>
       <c r="H82" s="155" t="n">
-        <v>859.6852230815548</v>
+        <v>859.6852230815547</v>
       </c>
       <c r="I82" s="156" t="n">
-        <v>912.6434333836097</v>
+        <v>912.6434333836098</v>
       </c>
       <c r="J82" s="156" t="n">
         <v>955.3722709173509</v>
       </c>
       <c r="K82" s="156" t="n">
-        <v>993.868457005895</v>
+        <v>993.8684570058953</v>
       </c>
       <c r="L82" s="157" t="n">
-        <v>1019.629473250403</v>
+        <v>1019.629473250404</v>
       </c>
       <c r="M82" s="158" t="n">
-        <v>7229746.468434095</v>
+        <v>7229746.468434096</v>
       </c>
       <c r="N82" s="159" t="n">
-        <v>8374362.880356445</v>
+        <v>8374362.880356447</v>
       </c>
       <c r="O82" s="159" t="n">
         <v>9589173.485237585</v>
       </c>
       <c r="P82" s="159" t="n">
-        <v>11020125.78512698</v>
+        <v>11020125.78512699</v>
       </c>
       <c r="Q82" s="160" t="n">
         <v>12762593.22417804</v>
@@ -8628,7 +8628,7 @@
         <v>1220.118038004213</v>
       </c>
       <c r="X82" s="157" t="n">
-        <v>1251.743431058676</v>
+        <v>1251.743431058677</v>
       </c>
       <c r="Y82" s="155" t="n">
         <v>1054.992116134037</v>
@@ -8643,19 +8643,19 @@
         <v>1220.118038004213</v>
       </c>
       <c r="AC82" s="157" t="n">
-        <v>1251.743431058676</v>
+        <v>1251.743431058677</v>
       </c>
       <c r="AD82" s="158" t="n">
-        <v>7229746.468434095</v>
+        <v>7229746.468434096</v>
       </c>
       <c r="AE82" s="159" t="n">
-        <v>8374362.880356445</v>
+        <v>8374362.880356447</v>
       </c>
       <c r="AF82" s="159" t="n">
         <v>9589173.485237585</v>
       </c>
       <c r="AG82" s="159" t="n">
-        <v>11020125.78512698</v>
+        <v>11020125.78512699</v>
       </c>
       <c r="AH82" s="160" t="n">
         <v>12762593.22417804</v>
@@ -8668,16 +8668,16 @@
         </is>
       </c>
       <c r="C83" s="161" t="n">
-        <v>550.0115829396109</v>
+        <v>550.0115829396108</v>
       </c>
       <c r="D83" s="162" t="n">
-        <v>589.7559092826018</v>
+        <v>589.7559092826017</v>
       </c>
       <c r="E83" s="162" t="n">
-        <v>629.0114830078666</v>
+        <v>629.0114830078664</v>
       </c>
       <c r="F83" s="162" t="n">
-        <v>668.8046977612812</v>
+        <v>668.8046977612813</v>
       </c>
       <c r="G83" s="163" t="n">
         <v>703.4075405758583</v>
@@ -8686,13 +8686,13 @@
         <v>545.2139750160378</v>
       </c>
       <c r="I83" s="162" t="n">
-        <v>586.0059974071315</v>
+        <v>586.0059974071314</v>
       </c>
       <c r="J83" s="162" t="n">
-        <v>626.3502865034189</v>
+        <v>626.3502865034188</v>
       </c>
       <c r="K83" s="162" t="n">
-        <v>667.2800845108518</v>
+        <v>667.2800845108519</v>
       </c>
       <c r="L83" s="163" t="n">
         <v>703.1535551384234</v>
@@ -8718,22 +8718,22 @@
         </is>
       </c>
       <c r="T83" s="161" t="n">
-        <v>651.2029683971482</v>
+        <v>651.2029683971481</v>
       </c>
       <c r="U83" s="162" t="n">
         <v>698.8373664694631</v>
       </c>
       <c r="V83" s="162" t="n">
-        <v>745.6840252237787</v>
+        <v>745.6840252237786</v>
       </c>
       <c r="W83" s="162" t="n">
-        <v>793.0798809240357</v>
+        <v>793.0798809240356</v>
       </c>
       <c r="X83" s="163" t="n">
         <v>834.3213273028758</v>
       </c>
       <c r="Y83" s="161" t="n">
-        <v>645.5312148738194</v>
+        <v>645.5312148738193</v>
       </c>
       <c r="Z83" s="162" t="n">
         <v>694.3938430720161</v>
@@ -8742,7 +8742,7 @@
         <v>742.5237184298113</v>
       </c>
       <c r="AB83" s="162" t="n">
-        <v>791.2604097191262</v>
+        <v>791.2604097191261</v>
       </c>
       <c r="AC83" s="163" t="n">
         <v>834.0006078507124</v>
@@ -8770,49 +8770,49 @@
         </is>
       </c>
       <c r="C84" s="155" t="n">
-        <v>6427.932072436402</v>
+        <v>6427.932072436399</v>
       </c>
       <c r="D84" s="156" t="n">
-        <v>6697.206360277312</v>
+        <v>6697.206360277311</v>
       </c>
       <c r="E84" s="156" t="n">
-        <v>7046.892393719898</v>
+        <v>7046.892393719897</v>
       </c>
       <c r="F84" s="156" t="n">
-        <v>7326.464733788702</v>
+        <v>7326.464733788699</v>
       </c>
       <c r="G84" s="157" t="n">
-        <v>7637.137634855172</v>
+        <v>7637.137634855169</v>
       </c>
       <c r="H84" s="155" t="n">
-        <v>6425.379721480364</v>
+        <v>6425.37972148036</v>
       </c>
       <c r="I84" s="156" t="n">
-        <v>6694.803334925235</v>
+        <v>6694.803334925234</v>
       </c>
       <c r="J84" s="156" t="n">
         <v>7044.576352856699</v>
       </c>
       <c r="K84" s="156" t="n">
-        <v>7324.311372986042</v>
+        <v>7324.311372986039</v>
       </c>
       <c r="L84" s="157" t="n">
-        <v>7635.140664953097</v>
+        <v>7635.140664953095</v>
       </c>
       <c r="M84" s="158" t="n">
-        <v>59943029.59379704</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="N84" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="O84" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="P84" s="159" t="n">
-        <v>96436610.61872099</v>
+        <v>96436610.61872096</v>
       </c>
       <c r="Q84" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
       <c r="S84" s="32" t="inlineStr">
         <is>
@@ -8820,49 +8820,49 @@
         </is>
       </c>
       <c r="T84" s="155" t="n">
-        <v>3902.366969719231</v>
+        <v>3902.366969719229</v>
       </c>
       <c r="U84" s="156" t="n">
-        <v>4065.842108352229</v>
+        <v>4065.842108352228</v>
       </c>
       <c r="V84" s="156" t="n">
-        <v>4278.134835048896</v>
+        <v>4278.134835048895</v>
       </c>
       <c r="W84" s="156" t="n">
-        <v>4447.86187217953</v>
+        <v>4447.861872179529</v>
       </c>
       <c r="X84" s="157" t="n">
-        <v>4636.469911879788</v>
+        <v>4636.469911879786</v>
       </c>
       <c r="Y84" s="155" t="n">
-        <v>3901.303136345263</v>
+        <v>3901.303136345261</v>
       </c>
       <c r="Z84" s="156" t="n">
-        <v>4064.840526696178</v>
+        <v>4064.840526696177</v>
       </c>
       <c r="AA84" s="156" t="n">
-        <v>4277.169517678468</v>
+        <v>4277.169517678467</v>
       </c>
       <c r="AB84" s="156" t="n">
-        <v>4446.96436904227</v>
+        <v>4446.964369042269</v>
       </c>
       <c r="AC84" s="157" t="n">
-        <v>4635.637599652919</v>
+        <v>4635.637599652917</v>
       </c>
       <c r="AD84" s="158" t="n">
-        <v>59943029.59379704</v>
+        <v>59943029.59379701</v>
       </c>
       <c r="AE84" s="159" t="n">
-        <v>69981356.14272326</v>
+        <v>69981356.14272325</v>
       </c>
       <c r="AF84" s="159" t="n">
-        <v>81958614.52098852</v>
+        <v>81958614.52098851</v>
       </c>
       <c r="AG84" s="159" t="n">
-        <v>96436610.61872099</v>
+        <v>96436610.61872096</v>
       </c>
       <c r="AH84" s="160" t="n">
-        <v>114364777.8253523</v>
+        <v>114364777.8253522</v>
       </c>
     </row>
     <row r="85" ht="15.6" customHeight="1" thickBot="1" thickTop="1">
@@ -8872,10 +8872,10 @@
         </is>
       </c>
       <c r="C85" s="179" t="n">
-        <v>907.3726468453527</v>
+        <v>907.3726468453522</v>
       </c>
       <c r="D85" s="180" t="n">
-        <v>971.1018187164211</v>
+        <v>971.1018187164209</v>
       </c>
       <c r="E85" s="180" t="n">
         <v>1041.427129836327</v>
@@ -8887,22 +8887,22 @@
         <v>1184.283010822623</v>
       </c>
       <c r="H85" s="179" t="n">
-        <v>899.9135680551137</v>
+        <v>899.9135680551134</v>
       </c>
       <c r="I85" s="180" t="n">
-        <v>965.2888904893565</v>
+        <v>965.2888904893563</v>
       </c>
       <c r="J85" s="180" t="n">
         <v>1037.281286041056</v>
       </c>
       <c r="K85" s="180" t="n">
-        <v>1113.986814391712</v>
+        <v>1113.986814391711</v>
       </c>
       <c r="L85" s="181" t="n">
         <v>1183.863571047504</v>
       </c>
       <c r="M85" s="182" t="n">
-        <v>139177672.0640352</v>
+        <v>139177672.0640351</v>
       </c>
       <c r="N85" s="183" t="n">
         <v>162515317.5536343</v>
@@ -8922,7 +8922,7 @@
         </is>
       </c>
       <c r="T85" s="185" t="n">
-        <v>1015.636319267229</v>
+        <v>1015.636319267228</v>
       </c>
       <c r="U85" s="186" t="n">
         <v>1086.163050918508</v>
@@ -8931,13 +8931,13 @@
         <v>1163.372783248337</v>
       </c>
       <c r="W85" s="186" t="n">
-        <v>1244.097075718279</v>
+        <v>1244.097075718278</v>
       </c>
       <c r="X85" s="187" t="n">
         <v>1317.544480787878</v>
       </c>
       <c r="Y85" s="185" t="n">
-        <v>1007.743795367484</v>
+        <v>1007.743795367483</v>
       </c>
       <c r="Z85" s="186" t="n">
         <v>1080.016294266431</v>
@@ -8952,7 +8952,7 @@
         <v>1317.072309850426</v>
       </c>
       <c r="AD85" s="188" t="n">
-        <v>139177672.0640352</v>
+        <v>139177672.0640351</v>
       </c>
       <c r="AE85" s="189" t="n">
         <v>162515317.5536343</v>
@@ -9331,10 +9331,10 @@
         </is>
       </c>
       <c r="T90" s="74" t="n">
-        <v>90770.18477882954</v>
+        <v>90770.18477882956</v>
       </c>
       <c r="U90" s="75" t="n">
-        <v>99350.30131074588</v>
+        <v>99350.3013107459</v>
       </c>
       <c r="V90" s="75" t="n">
         <v>107413.1502734667</v>
@@ -9361,10 +9361,10 @@
         <v>30.33146387675285</v>
       </c>
       <c r="AD90" s="74" t="n">
-        <v>91572.11847410812</v>
+        <v>91572.11847410814</v>
       </c>
       <c r="AE90" s="75" t="n">
-        <v>99985.81090161098</v>
+        <v>99985.810901611</v>
       </c>
       <c r="AF90" s="75" t="n">
         <v>107869.4930351635</v>
@@ -9404,19 +9404,19 @@
         </is>
       </c>
       <c r="C91" s="79" t="n">
-        <v>24363.46566804107</v>
+        <v>24363.46566804108</v>
       </c>
       <c r="D91" s="80" t="n">
-        <v>25902.71885808726</v>
+        <v>25902.71885808727</v>
       </c>
       <c r="E91" s="80" t="n">
         <v>27594.28627823325</v>
       </c>
       <c r="F91" s="80" t="n">
-        <v>29509.54823003766</v>
+        <v>29509.54823003767</v>
       </c>
       <c r="G91" s="81" t="n">
-        <v>32225.47504670375</v>
+        <v>32225.47504670376</v>
       </c>
       <c r="H91" s="79" t="n">
         <v>234.6275246081198</v>
@@ -9434,19 +9434,19 @@
         <v>34.93811261153121</v>
       </c>
       <c r="M91" s="79" t="n">
-        <v>24598.09319264919</v>
+        <v>24598.0931926492</v>
       </c>
       <c r="N91" s="80" t="n">
         <v>26094.00600724539</v>
       </c>
       <c r="O91" s="80" t="n">
-        <v>27739.06644940479</v>
+        <v>27739.0664494048</v>
       </c>
       <c r="P91" s="80" t="n">
         <v>29603.54742399331</v>
       </c>
       <c r="Q91" s="81" t="n">
-        <v>32260.41315931528</v>
+        <v>32260.41315931529</v>
       </c>
       <c r="S91" s="32" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>24084.48333297903</v>
       </c>
       <c r="U91" s="80" t="n">
-        <v>25606.11076915827</v>
+        <v>25606.11076915828</v>
       </c>
       <c r="V91" s="80" t="n">
         <v>27278.30830838431</v>
@@ -9484,10 +9484,10 @@
         <v>34.81840391551756</v>
       </c>
       <c r="AD91" s="79" t="n">
-        <v>24318.30695168267</v>
+        <v>24318.30695168268</v>
       </c>
       <c r="AE91" s="80" t="n">
-        <v>25796.74250983899</v>
+        <v>25796.742509839</v>
       </c>
       <c r="AF91" s="80" t="n">
         <v>27422.59241825763</v>
@@ -9496,7 +9496,7 @@
         <v>29265.31601112272</v>
       </c>
       <c r="AH91" s="81" t="n">
-        <v>31891.2844434645</v>
+        <v>31891.28444346451</v>
       </c>
       <c r="AJ91" s="120" t="n">
         <v>88.96942370606493</v>
@@ -9533,7 +9533,7 @@
         <v>159330.3717431031</v>
       </c>
       <c r="F92" s="86" t="n">
-        <v>171543.4305004976</v>
+        <v>171543.4305004977</v>
       </c>
       <c r="G92" s="87" t="n">
         <v>188429.8307206147</v>
@@ -9563,7 +9563,7 @@
         <v>160041.5382581457</v>
       </c>
       <c r="P92" s="86" t="n">
-        <v>171960.7102570369</v>
+        <v>171960.710257037</v>
       </c>
       <c r="Q92" s="87" t="n">
         <v>188502.4144986588</v>
@@ -9583,7 +9583,7 @@
         <v>134691.458581851</v>
       </c>
       <c r="W92" s="86" t="n">
-        <v>144981.264521751</v>
+        <v>144981.2645217511</v>
       </c>
       <c r="X92" s="87" t="n">
         <v>159220.2166031419</v>
@@ -9636,7 +9636,7 @@
         </is>
       </c>
       <c r="C93" s="79" t="n">
-        <v>8372.046597771947</v>
+        <v>8372.046597771949</v>
       </c>
       <c r="D93" s="80" t="n">
         <v>9151.95398242366</v>
@@ -9666,7 +9666,7 @@
         <v>0</v>
       </c>
       <c r="M93" s="79" t="n">
-        <v>8409.760077670009</v>
+        <v>8409.760077670011</v>
       </c>
       <c r="N93" s="80" t="n">
         <v>9175.941637259844</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="T93" s="79" t="n">
-        <v>6819.596772554498</v>
+        <v>6819.5967725545</v>
       </c>
       <c r="U93" s="80" t="n">
         <v>7454.88395366953</v>
@@ -9695,7 +9695,7 @@
         <v>8169.062008648177</v>
       </c>
       <c r="W93" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>9032.016118008522</v>
       </c>
       <c r="X93" s="81" t="n">
         <v>10195.85396456519</v>
@@ -9716,7 +9716,7 @@
         <v>0</v>
       </c>
       <c r="AD93" s="79" t="n">
-        <v>6852.891465129731</v>
+        <v>6852.891465129733</v>
       </c>
       <c r="AE93" s="80" t="n">
         <v>7476.061039303906</v>
@@ -9725,7 +9725,7 @@
         <v>8176.473725753166</v>
       </c>
       <c r="AG93" s="80" t="n">
-        <v>9032.01611800852</v>
+        <v>9032.016118008522</v>
       </c>
       <c r="AH93" s="81" t="n">
         <v>10195.85396456519</v>
@@ -9759,7 +9759,7 @@
         <v>144059.9524227434</v>
       </c>
       <c r="D94" s="86" t="n">
-        <v>156902.135196021</v>
+        <v>156902.1351960211</v>
       </c>
       <c r="E94" s="86" t="n">
         <v>169359.0831284644</v>
@@ -9815,7 +9815,7 @@
         <v>142860.5205904992</v>
       </c>
       <c r="W94" s="86" t="n">
-        <v>154013.2806397595</v>
+        <v>154013.2806397596</v>
       </c>
       <c r="X94" s="87" t="n">
         <v>169416.0705677071</v>
@@ -9824,7 +9824,7 @@
         <v>1069.052006557457</v>
       </c>
       <c r="Z94" s="86" t="n">
-        <v>847.3184171802002</v>
+        <v>847.3184171802003</v>
       </c>
       <c r="AA94" s="86" t="n">
         <v>608.0385886751235</v>
@@ -9845,7 +9845,7 @@
         <v>143468.5591791743</v>
       </c>
       <c r="AG94" s="86" t="n">
-        <v>154367.427929142</v>
+        <v>154367.4279291421</v>
       </c>
       <c r="AH94" s="87" t="n">
         <v>169481.2204354994</v>
@@ -9991,7 +9991,7 @@
         <v>153385.3511541392</v>
       </c>
       <c r="D96" s="133" t="n">
-        <v>167351.4706917583</v>
+        <v>167351.4706917584</v>
       </c>
       <c r="E96" s="133" t="n">
         <v>180989.5451735538</v>
@@ -10027,7 +10027,7 @@
         <v>181712.930809605</v>
       </c>
       <c r="P96" s="133" t="n">
-        <v>196215.4686800105</v>
+        <v>196215.4686800106</v>
       </c>
       <c r="Q96" s="134" t="n">
         <v>215998.0465161036</v>
@@ -10038,7 +10038,7 @@
         </is>
       </c>
       <c r="T96" s="135" t="n">
-        <v>137034.9498376056</v>
+        <v>137034.9498376057</v>
       </c>
       <c r="U96" s="136" t="n">
         <v>149623.3161459545</v>
@@ -10047,7 +10047,7 @@
         <v>162018.0781900254</v>
       </c>
       <c r="W96" s="136" t="n">
-        <v>175694.8466123704</v>
+        <v>175694.8466123705</v>
       </c>
       <c r="X96" s="137" t="n">
         <v>194082.4180257854</v>
@@ -10056,7 +10056,7 @@
         <v>1073.240660637687</v>
       </c>
       <c r="Z96" s="136" t="n">
-        <v>851.5594798971542</v>
+        <v>851.5594798971543</v>
       </c>
       <c r="AA96" s="136" t="n">
         <v>612.3622712061436</v>
@@ -10077,7 +10077,7 @@
         <v>162630.4404612315</v>
       </c>
       <c r="AG96" s="136" t="n">
-        <v>176053.3697572503</v>
+        <v>176053.3697572504</v>
       </c>
       <c r="AH96" s="137" t="n">
         <v>194151.9966484447</v>
